--- a/Sindhi Muslim/Student Attendance/Class 1/Class 1 - Monthly Attendance - November-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/Class 1/Class 1 - Monthly Attendance - November-2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\Class 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF48058F-F79E-46DD-BDB5-1D5DDC38A4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C54913A-AA32-4A0C-B22B-7D3EE9E7CE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="542" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="133">
   <si>
     <t>S.No</t>
   </si>
@@ -412,9 +412,6 @@
     <t>SUNDAY - SUNDAY - SUNDAY</t>
   </si>
   <si>
-    <t>Monthly Attendence Month of October-2024</t>
-  </si>
-  <si>
     <t>P</t>
   </si>
   <si>
@@ -434,6 +431,9 @@
   </si>
   <si>
     <t>SUNDAY - SUNDAY - SUNDAY - SUNDAY</t>
+  </si>
+  <si>
+    <t>Monthly Attendence Month of November-2024</t>
   </si>
 </sst>
 </file>
@@ -718,14 +718,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -742,6 +736,9 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -751,9 +748,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -762,6 +756,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255"/>
@@ -777,7 +777,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill>
@@ -818,13 +818,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -844,32 +837,30 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -921,48 +912,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1287,97 +1236,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25"/>
-      <c r="AI1" s="25"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="38"/>
+      <c r="AD1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
+      <c r="A2" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="37"/>
+      <c r="AF2" s="37"/>
+      <c r="AG2" s="37"/>
+      <c r="AH2" s="37"/>
+      <c r="AI2" s="37"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="28" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1500,25 +1449,25 @@
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="AJ3" s="26" t="s">
+      <c r="AJ3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="26" t="s">
+      <c r="AK3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="27" t="s">
+      <c r="AL3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="28"/>
+      <c r="AM3" s="26"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="21">
         <v>45597</v>
       </c>
@@ -1609,8 +1558,8 @@
       <c r="AI4" s="21">
         <v>45626</v>
       </c>
-      <c r="AJ4" s="26"/>
-      <c r="AK4" s="26"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1635,71 +1584,77 @@
         <v>20</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H5" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="31" t="s">
         <v>124</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M5" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N5" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="O5" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="N5" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="O5" s="31" t="s">
         <v>124</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V5" s="31" t="s">
         <v>124</v>
       </c>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
-      <c r="Y5" s="35"/>
+      <c r="Y5" s="24"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
-      <c r="AC5" s="32" t="s">
+      <c r="AC5" s="31" t="s">
         <v>124</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
-      <c r="AF5" s="35"/>
+      <c r="AF5" s="24"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
       <c r="AI5" s="11"/>
       <c r="AJ5" s="5">
-        <f>COUNTIF(F5:AI5,"P")</f>
-        <v>10</v>
+        <f t="shared" ref="AJ5:AJ28" si="2">COUNTIF(F5:AI5,"P")</f>
+        <v>13</v>
       </c>
       <c r="AK5" s="5">
-        <f>COUNTIF(F5:AI5,"A")</f>
+        <f t="shared" ref="AK5:AK28" si="3">COUNTIF(F5:AI5,"A")</f>
         <v>0</v>
       </c>
       <c r="AL5" s="5" t="s">
@@ -1728,62 +1683,68 @@
         <v>20</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H6" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H6" s="32"/>
       <c r="I6" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="N6" s="37"/>
-      <c r="O6" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="N6" s="35"/>
+      <c r="O6" s="32"/>
       <c r="P6" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R6" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V6" s="32"/>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
-      <c r="Y6" s="35"/>
+      <c r="Y6" s="24"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="11"/>
-      <c r="AC6" s="33"/>
+      <c r="AC6" s="32"/>
       <c r="AD6" s="11"/>
       <c r="AE6" s="11"/>
-      <c r="AF6" s="35"/>
+      <c r="AF6" s="24"/>
       <c r="AG6" s="11"/>
       <c r="AH6" s="11"/>
       <c r="AI6" s="11"/>
       <c r="AJ6" s="5">
-        <f>COUNTIF(F6:AI6,"P")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK6" s="5">
-        <f>COUNTIF(F6:AI6,"A")</f>
-        <v>10</v>
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="AL6" s="5" t="s">
         <v>10</v>
@@ -1809,61 +1770,67 @@
         <v>20</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H7" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H7" s="32"/>
       <c r="I7" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N7" s="37"/>
-      <c r="O7" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N7" s="35"/>
+      <c r="O7" s="32"/>
       <c r="P7" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R7" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V7" s="32"/>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
-      <c r="Y7" s="35"/>
+      <c r="Y7" s="24"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="11"/>
       <c r="AB7" s="11"/>
-      <c r="AC7" s="33"/>
+      <c r="AC7" s="32"/>
       <c r="AD7" s="11"/>
       <c r="AE7" s="11"/>
-      <c r="AF7" s="35"/>
+      <c r="AF7" s="24"/>
       <c r="AG7" s="11"/>
       <c r="AH7" s="11"/>
       <c r="AI7" s="11"/>
       <c r="AJ7" s="5">
-        <f>COUNTIF(F7:AI7,"P")</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>13</v>
       </c>
       <c r="AK7" s="5">
-        <f>COUNTIF(F7:AI7,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL7" s="3"/>
@@ -1886,69 +1853,75 @@
         <v>20</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H8" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H8" s="32"/>
       <c r="I8" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N8" s="37"/>
-      <c r="O8" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N8" s="35"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R8" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V8" s="32"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
-      <c r="Y8" s="35"/>
+      <c r="Y8" s="24"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="11"/>
       <c r="AB8" s="11"/>
-      <c r="AC8" s="33"/>
+      <c r="AC8" s="32"/>
       <c r="AD8" s="11"/>
       <c r="AE8" s="11"/>
-      <c r="AF8" s="35"/>
+      <c r="AF8" s="24"/>
       <c r="AG8" s="11"/>
       <c r="AH8" s="11"/>
       <c r="AI8" s="11"/>
       <c r="AJ8" s="5">
-        <f>COUNTIF(F8:AI8,"P")</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>13</v>
       </c>
       <c r="AK8" s="5">
-        <f>COUNTIF(F8:AI8,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AL8" s="27" t="s">
+      <c r="AL8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="28"/>
-      <c r="AN8" s="28"/>
-      <c r="AO8" s="29"/>
+      <c r="AM8" s="26"/>
+      <c r="AN8" s="26"/>
+      <c r="AO8" s="27"/>
     </row>
     <row r="9" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -1965,61 +1938,67 @@
         <v>20</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H9" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H9" s="32"/>
       <c r="I9" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M9" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N9" s="37"/>
-      <c r="O9" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N9" s="35"/>
+      <c r="O9" s="32"/>
       <c r="P9" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R9" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V9" s="32"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
-      <c r="Y9" s="35"/>
+      <c r="Y9" s="24"/>
       <c r="Z9" s="11"/>
       <c r="AA9" s="11"/>
       <c r="AB9" s="11"/>
-      <c r="AC9" s="33"/>
+      <c r="AC9" s="32"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
-      <c r="AF9" s="35"/>
+      <c r="AF9" s="24"/>
       <c r="AG9" s="11"/>
       <c r="AH9" s="11"/>
       <c r="AI9" s="11"/>
       <c r="AJ9" s="5">
-        <f>COUNTIF(F9:AI9,"P")</f>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>12</v>
       </c>
       <c r="AK9" s="5">
-        <f>COUNTIF(F9:AI9,"A")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AL9" s="5" t="s">
@@ -2050,62 +2029,68 @@
         <v>20</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H10" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H10" s="32"/>
       <c r="I10" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M10" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="N10" s="37"/>
-      <c r="O10" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="N10" s="35"/>
+      <c r="O10" s="32"/>
       <c r="P10" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T10" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V10" s="32"/>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
-      <c r="Y10" s="35"/>
+      <c r="Y10" s="24"/>
       <c r="Z10" s="11"/>
       <c r="AA10" s="11"/>
       <c r="AB10" s="11"/>
-      <c r="AC10" s="33"/>
+      <c r="AC10" s="32"/>
       <c r="AD10" s="11"/>
       <c r="AE10" s="11"/>
-      <c r="AF10" s="35"/>
+      <c r="AF10" s="24"/>
       <c r="AG10" s="11"/>
       <c r="AH10" s="11"/>
       <c r="AI10" s="11"/>
       <c r="AJ10" s="5">
-        <f>COUNTIF(F10:AI10,"P")</f>
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>9</v>
       </c>
       <c r="AK10" s="5">
-        <f>COUNTIF(F10:AI10,"A")</f>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="AL10" s="5" t="s">
         <v>16</v>
@@ -2138,61 +2123,67 @@
         <v>20</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H11" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H11" s="32"/>
       <c r="I11" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M11" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N11" s="37"/>
-      <c r="O11" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N11" s="35"/>
+      <c r="O11" s="32"/>
       <c r="P11" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q11" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R11" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V11" s="32"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
-      <c r="Y11" s="35"/>
+      <c r="Y11" s="24"/>
       <c r="Z11" s="11"/>
       <c r="AA11" s="11"/>
       <c r="AB11" s="11"/>
-      <c r="AC11" s="33"/>
+      <c r="AC11" s="32"/>
       <c r="AD11" s="11"/>
       <c r="AE11" s="11"/>
-      <c r="AF11" s="35"/>
+      <c r="AF11" s="24"/>
       <c r="AG11" s="11"/>
       <c r="AH11" s="11"/>
       <c r="AI11" s="11"/>
       <c r="AJ11" s="5">
-        <f>COUNTIF(F11:AI11,"P")</f>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>12</v>
       </c>
       <c r="AK11" s="5">
-        <f>COUNTIF(F11:AI11,"A")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AL11" s="5" t="s">
@@ -2200,15 +2191,15 @@
       </c>
       <c r="AM11" s="12">
         <f>AJ6+AJ7+AJ8+AJ11+AJ12+AJ13+AJ15+AJ19+AJ20+AJ21+AJ22+AJ23+AJ24+AJ25+AJ26+AJ28</f>
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="AN11" s="12">
         <f>AJ5+AJ9+AJ10+AJ14+AJ16+AJ17+AJ18+AJ27</f>
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="AO11" s="12">
         <f>AM11+AN11</f>
-        <v>194</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -2226,61 +2217,67 @@
         <v>20</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H12" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H12" s="32"/>
       <c r="I12" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N12" s="37"/>
-      <c r="O12" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N12" s="35"/>
+      <c r="O12" s="32"/>
       <c r="P12" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R12" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V12" s="32"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
-      <c r="Y12" s="35"/>
+      <c r="Y12" s="24"/>
       <c r="Z12" s="11"/>
       <c r="AA12" s="11"/>
       <c r="AB12" s="11"/>
-      <c r="AC12" s="33"/>
+      <c r="AC12" s="32"/>
       <c r="AD12" s="11"/>
       <c r="AE12" s="11"/>
-      <c r="AF12" s="35"/>
+      <c r="AF12" s="24"/>
       <c r="AG12" s="11"/>
       <c r="AH12" s="11"/>
       <c r="AI12" s="11"/>
       <c r="AJ12" s="5">
-        <f>COUNTIF(F12:AI12,"P")</f>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>12</v>
       </c>
       <c r="AK12" s="5">
-        <f>COUNTIF(F12:AI12,"A")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AL12" s="5" t="s">
@@ -2288,15 +2285,15 @@
       </c>
       <c r="AM12" s="12">
         <f>AM11/AM10</f>
-        <v>0.26518218623481782</v>
+        <v>0.33603238866396762</v>
       </c>
       <c r="AN12" s="12">
         <f>AN11/AN10</f>
-        <v>0.11538461538461539</v>
+        <v>0.14835164835164835</v>
       </c>
       <c r="AO12" s="12">
         <f>AO11/AO10</f>
-        <v>0.18653846153846154</v>
+        <v>0.23749999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -2314,61 +2311,67 @@
         <v>20</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H13" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H13" s="32"/>
       <c r="I13" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M13" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N13" s="37"/>
-      <c r="O13" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N13" s="35"/>
+      <c r="O13" s="32"/>
       <c r="P13" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R13" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V13" s="32"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
-      <c r="Y13" s="35"/>
+      <c r="Y13" s="24"/>
       <c r="Z13" s="11"/>
       <c r="AA13" s="11"/>
       <c r="AB13" s="11"/>
-      <c r="AC13" s="33"/>
+      <c r="AC13" s="32"/>
       <c r="AD13" s="11"/>
       <c r="AE13" s="11"/>
-      <c r="AF13" s="35"/>
+      <c r="AF13" s="24"/>
       <c r="AG13" s="11"/>
       <c r="AH13" s="11"/>
       <c r="AI13" s="11"/>
       <c r="AJ13" s="5">
-        <f>COUNTIF(F13:AI13,"P")</f>
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>9</v>
       </c>
       <c r="AK13" s="5">
-        <f>COUNTIF(F13:AI13,"A")</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="AL13" s="3"/>
@@ -2391,61 +2394,67 @@
         <v>20</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H14" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H14" s="32"/>
       <c r="I14" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K14" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M14" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N14" s="37"/>
-      <c r="O14" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N14" s="35"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R14" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V14" s="32"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
-      <c r="Y14" s="35"/>
+      <c r="Y14" s="24"/>
       <c r="Z14" s="11"/>
       <c r="AA14" s="11"/>
       <c r="AB14" s="11"/>
-      <c r="AC14" s="33"/>
+      <c r="AC14" s="32"/>
       <c r="AD14" s="11"/>
       <c r="AE14" s="11"/>
-      <c r="AF14" s="35"/>
+      <c r="AF14" s="24"/>
       <c r="AG14" s="11"/>
       <c r="AH14" s="11"/>
       <c r="AI14" s="11"/>
       <c r="AJ14" s="5">
-        <f>COUNTIF(F14:AI14,"P")</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
       <c r="AK14" s="5">
-        <f>COUNTIF(F14:AI14,"A")</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="AL14" s="19"/>
@@ -2468,61 +2477,67 @@
         <v>20</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H15" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H15" s="32"/>
       <c r="I15" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N15" s="37"/>
-      <c r="O15" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N15" s="35"/>
+      <c r="O15" s="32"/>
       <c r="P15" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V15" s="32"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
-      <c r="Y15" s="35"/>
+      <c r="Y15" s="24"/>
       <c r="Z15" s="11"/>
       <c r="AA15" s="11"/>
       <c r="AB15" s="11"/>
-      <c r="AC15" s="33"/>
+      <c r="AC15" s="32"/>
       <c r="AD15" s="11"/>
       <c r="AE15" s="11"/>
-      <c r="AF15" s="35"/>
+      <c r="AF15" s="24"/>
       <c r="AG15" s="11"/>
       <c r="AH15" s="11"/>
       <c r="AI15" s="11"/>
       <c r="AJ15" s="5">
-        <f>COUNTIF(F15:AI15,"P")</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>13</v>
       </c>
       <c r="AK15" s="5">
-        <f>COUNTIF(F15:AI15,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL15" s="3"/>
@@ -2545,69 +2560,75 @@
         <v>20</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H16" s="32"/>
       <c r="I16" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M16" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="N16" s="37"/>
-      <c r="O16" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="N16" s="35"/>
+      <c r="O16" s="32"/>
       <c r="P16" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q16" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T16" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V16" s="32"/>
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
-      <c r="Y16" s="35"/>
+      <c r="Y16" s="24"/>
       <c r="Z16" s="11"/>
       <c r="AA16" s="11"/>
       <c r="AB16" s="11"/>
-      <c r="AC16" s="33"/>
+      <c r="AC16" s="32"/>
       <c r="AD16" s="11"/>
       <c r="AE16" s="11"/>
-      <c r="AF16" s="35"/>
+      <c r="AF16" s="24"/>
       <c r="AG16" s="11"/>
       <c r="AH16" s="11"/>
       <c r="AI16" s="11"/>
       <c r="AJ16" s="5">
-        <f>COUNTIF(F16:AI16,"P")</f>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="AK16" s="5">
-        <f>COUNTIF(F16:AI16,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="AL16" s="27" t="s">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="AL16" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="28"/>
-      <c r="AN16" s="28"/>
-      <c r="AO16" s="29"/>
+      <c r="AM16" s="26"/>
+      <c r="AN16" s="26"/>
+      <c r="AO16" s="27"/>
     </row>
     <row r="17" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -2624,61 +2645,67 @@
         <v>20</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H17" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H17" s="32"/>
       <c r="I17" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M17" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N17" s="37"/>
-      <c r="O17" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N17" s="35"/>
+      <c r="O17" s="32"/>
       <c r="P17" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q17" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R17" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V17" s="32"/>
       <c r="W17" s="11"/>
       <c r="X17" s="11"/>
-      <c r="Y17" s="35"/>
+      <c r="Y17" s="24"/>
       <c r="Z17" s="11"/>
       <c r="AA17" s="11"/>
       <c r="AB17" s="11"/>
-      <c r="AC17" s="33"/>
+      <c r="AC17" s="32"/>
       <c r="AD17" s="11"/>
       <c r="AE17" s="11"/>
-      <c r="AF17" s="35"/>
+      <c r="AF17" s="24"/>
       <c r="AG17" s="11"/>
       <c r="AH17" s="11"/>
       <c r="AI17" s="11"/>
       <c r="AJ17" s="5">
-        <f>COUNTIF(F17:AI17,"P")</f>
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>10</v>
       </c>
       <c r="AK17" s="5">
-        <f>COUNTIF(F17:AI17,"A")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="AL17" s="5" t="s">
@@ -2709,62 +2736,68 @@
         <v>20</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H18" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H18" s="32"/>
       <c r="I18" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M18" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N18" s="37"/>
-      <c r="O18" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N18" s="35"/>
+      <c r="O18" s="32"/>
       <c r="P18" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R18" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V18" s="32"/>
       <c r="W18" s="11"/>
       <c r="X18" s="11"/>
-      <c r="Y18" s="35"/>
+      <c r="Y18" s="24"/>
       <c r="Z18" s="11"/>
       <c r="AA18" s="11"/>
       <c r="AB18" s="11"/>
-      <c r="AC18" s="33"/>
+      <c r="AC18" s="32"/>
       <c r="AD18" s="11"/>
       <c r="AE18" s="11"/>
-      <c r="AF18" s="35"/>
+      <c r="AF18" s="24"/>
       <c r="AG18" s="11"/>
       <c r="AH18" s="11"/>
       <c r="AI18" s="11"/>
       <c r="AJ18" s="5">
-        <f>COUNTIF(F18:AI18,"P")</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="AK18" s="5">
-        <f>COUNTIF(F18:AI18,"A")</f>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AL18" s="5" t="s">
         <v>16</v>
@@ -2797,77 +2830,83 @@
         <v>20</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H19" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H19" s="32"/>
       <c r="I19" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M19" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="N19" s="37"/>
-      <c r="O19" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="N19" s="35"/>
+      <c r="O19" s="32"/>
       <c r="P19" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="S19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="T19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V19" s="32"/>
       <c r="W19" s="11"/>
       <c r="X19" s="11"/>
-      <c r="Y19" s="35"/>
+      <c r="Y19" s="24"/>
       <c r="Z19" s="11"/>
       <c r="AA19" s="11"/>
       <c r="AB19" s="11"/>
-      <c r="AC19" s="33"/>
+      <c r="AC19" s="32"/>
       <c r="AD19" s="11"/>
       <c r="AE19" s="11"/>
-      <c r="AF19" s="35"/>
+      <c r="AF19" s="24"/>
       <c r="AG19" s="11"/>
       <c r="AH19" s="11"/>
       <c r="AI19" s="11"/>
       <c r="AJ19" s="5">
-        <f>COUNTIF(F19:AI19,"P")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="AK19" s="5">
-        <f>COUNTIF(F19:AI19,"A")</f>
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="AL19" s="5" t="s">
         <v>19</v>
       </c>
       <c r="AM19" s="12">
         <f>AM18-AM11</f>
-        <v>363</v>
+        <v>328</v>
       </c>
       <c r="AN19" s="12">
         <f>AN18-AN11</f>
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="AO19" s="12">
         <f>AM19+AN19</f>
-        <v>846</v>
+        <v>793</v>
       </c>
     </row>
     <row r="20" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -2885,77 +2924,83 @@
         <v>20</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H20" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H20" s="32"/>
       <c r="I20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M20" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N20" s="37"/>
-      <c r="O20" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N20" s="35"/>
+      <c r="O20" s="32"/>
       <c r="P20" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T20" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V20" s="32"/>
       <c r="W20" s="11"/>
       <c r="X20" s="11"/>
-      <c r="Y20" s="35"/>
+      <c r="Y20" s="24"/>
       <c r="Z20" s="11"/>
       <c r="AA20" s="11"/>
       <c r="AB20" s="11"/>
-      <c r="AC20" s="33"/>
+      <c r="AC20" s="32"/>
       <c r="AD20" s="11"/>
       <c r="AE20" s="11"/>
-      <c r="AF20" s="35"/>
+      <c r="AF20" s="24"/>
       <c r="AG20" s="11"/>
       <c r="AH20" s="11"/>
       <c r="AI20" s="11"/>
       <c r="AJ20" s="5">
-        <f>COUNTIF(F20:AI20,"P")</f>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="AK20" s="5">
-        <f>COUNTIF(F20:AI20,"A")</f>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AL20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AM20" s="20">
         <f>AM19/AM18</f>
-        <v>0.73481781376518218</v>
+        <v>0.66396761133603244</v>
       </c>
       <c r="AN20" s="20">
         <f>AN19/AN18</f>
-        <v>0.88461538461538458</v>
+        <v>0.85164835164835162</v>
       </c>
       <c r="AO20" s="20">
         <f>AO19/AO18</f>
-        <v>0.81346153846153846</v>
+        <v>0.76249999999999996</v>
       </c>
     </row>
     <row r="21" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -2973,62 +3018,68 @@
         <v>20</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H21" s="32"/>
       <c r="I21" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M21" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N21" s="37"/>
-      <c r="O21" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N21" s="35"/>
+      <c r="O21" s="32"/>
       <c r="P21" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q21" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T21" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V21" s="32"/>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
-      <c r="Y21" s="35"/>
+      <c r="Y21" s="24"/>
       <c r="Z21" s="11"/>
       <c r="AA21" s="11"/>
       <c r="AB21" s="11"/>
-      <c r="AC21" s="33"/>
+      <c r="AC21" s="32"/>
       <c r="AD21" s="11"/>
       <c r="AE21" s="11"/>
-      <c r="AF21" s="35"/>
+      <c r="AF21" s="24"/>
       <c r="AG21" s="11"/>
       <c r="AH21" s="11"/>
       <c r="AI21" s="11"/>
       <c r="AJ21" s="5">
-        <f>COUNTIF(F21:AI21,"P")</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>12</v>
       </c>
       <c r="AK21" s="5">
-        <f>COUNTIF(F21:AI21,"A")</f>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3046,62 +3097,68 @@
         <v>20</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H22" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H22" s="32"/>
       <c r="I22" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M22" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N22" s="37"/>
-      <c r="O22" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N22" s="35"/>
+      <c r="O22" s="32"/>
       <c r="P22" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R22" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T22" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V22" s="32"/>
       <c r="W22" s="11"/>
       <c r="X22" s="11"/>
-      <c r="Y22" s="35"/>
+      <c r="Y22" s="24"/>
       <c r="Z22" s="11"/>
       <c r="AA22" s="11"/>
       <c r="AB22" s="11"/>
-      <c r="AC22" s="33"/>
+      <c r="AC22" s="32"/>
       <c r="AD22" s="11"/>
       <c r="AE22" s="11"/>
-      <c r="AF22" s="35"/>
+      <c r="AF22" s="24"/>
       <c r="AG22" s="11"/>
       <c r="AH22" s="11"/>
       <c r="AI22" s="11"/>
       <c r="AJ22" s="5">
-        <f>COUNTIF(F22:AI22,"P")</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="AK22" s="5">
-        <f>COUNTIF(F22:AI22,"A")</f>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3119,61 +3176,67 @@
         <v>20</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H23" s="32"/>
       <c r="I23" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M23" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="N23" s="37"/>
-      <c r="O23" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="N23" s="35"/>
+      <c r="O23" s="32"/>
       <c r="P23" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q23" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S23" s="11"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V23" s="32"/>
       <c r="W23" s="11"/>
       <c r="X23" s="11"/>
-      <c r="Y23" s="35"/>
+      <c r="Y23" s="24"/>
       <c r="Z23" s="11"/>
       <c r="AA23" s="11"/>
       <c r="AB23" s="11"/>
-      <c r="AC23" s="33"/>
+      <c r="AC23" s="32"/>
       <c r="AD23" s="11"/>
       <c r="AE23" s="11"/>
-      <c r="AF23" s="35"/>
+      <c r="AF23" s="24"/>
       <c r="AG23" s="11"/>
       <c r="AH23" s="11"/>
       <c r="AI23" s="11"/>
       <c r="AJ23" s="5">
-        <f>COUNTIF(F23:AI23,"P")</f>
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>10</v>
       </c>
       <c r="AK23" s="5">
-        <f>COUNTIF(F23:AI23,"A")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -3192,61 +3255,67 @@
         <v>20</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H24" s="32"/>
       <c r="I24" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M24" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N24" s="37"/>
-      <c r="O24" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N24" s="35"/>
+      <c r="O24" s="32"/>
       <c r="P24" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q24" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V24" s="32"/>
       <c r="W24" s="11"/>
       <c r="X24" s="11"/>
-      <c r="Y24" s="35"/>
+      <c r="Y24" s="24"/>
       <c r="Z24" s="11"/>
       <c r="AA24" s="11"/>
       <c r="AB24" s="11"/>
-      <c r="AC24" s="33"/>
+      <c r="AC24" s="32"/>
       <c r="AD24" s="11"/>
       <c r="AE24" s="11"/>
-      <c r="AF24" s="35"/>
+      <c r="AF24" s="24"/>
       <c r="AG24" s="11"/>
       <c r="AH24" s="11"/>
       <c r="AI24" s="11"/>
       <c r="AJ24" s="5">
-        <f>COUNTIF(F24:AI24,"P")</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>13</v>
       </c>
       <c r="AK24" s="5">
-        <f>COUNTIF(F24:AI24,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3265,62 +3334,68 @@
         <v>20</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H25" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H25" s="32"/>
       <c r="I25" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M25" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N25" s="37"/>
-      <c r="O25" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N25" s="35"/>
+      <c r="O25" s="32"/>
       <c r="P25" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q25" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V25" s="32"/>
       <c r="W25" s="11"/>
       <c r="X25" s="11"/>
-      <c r="Y25" s="35"/>
+      <c r="Y25" s="24"/>
       <c r="Z25" s="11"/>
       <c r="AA25" s="11"/>
       <c r="AB25" s="11"/>
-      <c r="AC25" s="33"/>
+      <c r="AC25" s="32"/>
       <c r="AD25" s="11"/>
       <c r="AE25" s="11"/>
-      <c r="AF25" s="35"/>
+      <c r="AF25" s="24"/>
       <c r="AG25" s="11"/>
       <c r="AH25" s="11"/>
       <c r="AI25" s="11"/>
       <c r="AJ25" s="5">
-        <f>COUNTIF(F25:AI25,"P")</f>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="AK25" s="5">
-        <f>COUNTIF(F25:AI25,"A")</f>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3338,61 +3413,67 @@
         <v>20</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H26" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H26" s="32"/>
       <c r="I26" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M26" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N26" s="37"/>
-      <c r="O26" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N26" s="35"/>
+      <c r="O26" s="32"/>
       <c r="P26" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S26" s="11"/>
-      <c r="T26" s="11"/>
-      <c r="U26" s="11"/>
-      <c r="V26" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V26" s="32"/>
       <c r="W26" s="11"/>
       <c r="X26" s="11"/>
-      <c r="Y26" s="35"/>
+      <c r="Y26" s="24"/>
       <c r="Z26" s="11"/>
       <c r="AA26" s="11"/>
       <c r="AB26" s="11"/>
-      <c r="AC26" s="33"/>
+      <c r="AC26" s="32"/>
       <c r="AD26" s="11"/>
       <c r="AE26" s="11"/>
-      <c r="AF26" s="35"/>
+      <c r="AF26" s="24"/>
       <c r="AG26" s="11"/>
       <c r="AH26" s="11"/>
       <c r="AI26" s="11"/>
       <c r="AJ26" s="5">
-        <f>COUNTIF(F26:AI26,"P")</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>13</v>
       </c>
       <c r="AK26" s="5">
-        <f>COUNTIF(F26:AI26,"A")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3411,62 +3492,68 @@
         <v>20</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H27" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H27" s="32"/>
       <c r="I27" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M27" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N27" s="37"/>
-      <c r="O27" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="N27" s="35"/>
+      <c r="O27" s="32"/>
       <c r="P27" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="S27" s="11"/>
-      <c r="T27" s="11"/>
-      <c r="U27" s="11"/>
-      <c r="V27" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="S27" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="T27" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V27" s="32"/>
       <c r="W27" s="11"/>
       <c r="X27" s="11"/>
-      <c r="Y27" s="35"/>
+      <c r="Y27" s="24"/>
       <c r="Z27" s="11"/>
       <c r="AA27" s="11"/>
       <c r="AB27" s="11"/>
-      <c r="AC27" s="33"/>
+      <c r="AC27" s="32"/>
       <c r="AD27" s="11"/>
       <c r="AE27" s="11"/>
-      <c r="AF27" s="35"/>
+      <c r="AF27" s="24"/>
       <c r="AG27" s="11"/>
       <c r="AH27" s="11"/>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="5">
-        <f>COUNTIF(F27:AI27,"P")</f>
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
       <c r="AK27" s="5">
-        <f>COUNTIF(F27:AI27,"A")</f>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3484,62 +3571,68 @@
         <v>20</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H28" s="34"/>
+        <v>125</v>
+      </c>
+      <c r="H28" s="33"/>
       <c r="I28" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J28" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M28" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="N28" s="38"/>
-      <c r="O28" s="34"/>
+        <v>126</v>
+      </c>
+      <c r="N28" s="36"/>
+      <c r="O28" s="33"/>
       <c r="P28" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S28" s="11"/>
-      <c r="T28" s="11"/>
-      <c r="U28" s="11"/>
-      <c r="V28" s="34"/>
+        <v>125</v>
+      </c>
+      <c r="S28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T28" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U28" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V28" s="33"/>
       <c r="W28" s="11"/>
       <c r="X28" s="11"/>
-      <c r="Y28" s="35"/>
+      <c r="Y28" s="24"/>
       <c r="Z28" s="11"/>
       <c r="AA28" s="11"/>
       <c r="AB28" s="11"/>
-      <c r="AC28" s="34"/>
+      <c r="AC28" s="33"/>
       <c r="AD28" s="11"/>
       <c r="AE28" s="11"/>
-      <c r="AF28" s="35"/>
+      <c r="AF28" s="24"/>
       <c r="AG28" s="11"/>
       <c r="AH28" s="11"/>
       <c r="AI28" s="11"/>
       <c r="AJ28" s="5">
-        <f>COUNTIF(F28:AI28,"P")</f>
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
       <c r="AK28" s="5">
-        <f>COUNTIF(F28:AI28,"A")</f>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
@@ -3547,6 +3640,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A2:AI2"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AL8:AO8"/>
     <mergeCell ref="AL16:AO16"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -3559,43 +3657,8 @@
     <mergeCell ref="O5:O28"/>
     <mergeCell ref="V5:V28"/>
     <mergeCell ref="AC5:AC28"/>
-    <mergeCell ref="A2:AI2"/>
-    <mergeCell ref="A1:AI1"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AL8:AO8"/>
   </mergeCells>
-  <conditionalFormatting sqref="AJ3:AK3 AJ5:AK28">
-    <cfRule type="expression" dxfId="22" priority="26">
-      <formula>#REF!="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL5:AL6">
-    <cfRule type="expression" dxfId="21" priority="22">
-      <formula>AL$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL9:AL12">
-    <cfRule type="expression" dxfId="20" priority="16">
-      <formula>AL$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL17:AL20">
-    <cfRule type="expression" dxfId="19" priority="15">
-      <formula>AL$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM9:AO9">
-    <cfRule type="expression" dxfId="18" priority="17">
-      <formula>AM$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM17:AO17">
-    <cfRule type="expression" dxfId="17" priority="14">
-      <formula>AM$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AI4 F6:G28 I6:M28 P5:U28 F5:O5 W5:AB28 V5 AD5:AI28 AC5">
+  <conditionalFormatting sqref="F3:AI4 F5:O5 V5 AC5 P5:U28 W5:AB28 AD5:AI28 F6:G28 I6:M28">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"L"</formula>
     </cfRule>
@@ -3610,6 +3673,36 @@
     </cfRule>
     <cfRule type="expression" dxfId="12" priority="5">
       <formula>F$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ3:AK3 AJ5:AK28">
+    <cfRule type="expression" dxfId="11" priority="26">
+      <formula>#REF!="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL5:AL6">
+    <cfRule type="expression" dxfId="10" priority="22">
+      <formula>AL$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL9:AL12">
+    <cfRule type="expression" dxfId="9" priority="16">
+      <formula>AL$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL17:AL20">
+    <cfRule type="expression" dxfId="8" priority="15">
+      <formula>AL$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM9:AO9">
+    <cfRule type="expression" dxfId="7" priority="17">
+      <formula>AM$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM17:AO17">
+    <cfRule type="expression" dxfId="6" priority="14">
+      <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3664,97 +3757,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25"/>
-      <c r="AI1" s="25"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="38"/>
+      <c r="AD1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
+      <c r="A2" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="37"/>
+      <c r="AF2" s="37"/>
+      <c r="AG2" s="37"/>
+      <c r="AH2" s="37"/>
+      <c r="AI2" s="37"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="28" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -3877,25 +3970,25 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AJ3" s="26" t="s">
+      <c r="AJ3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="26" t="s">
+      <c r="AK3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="27" t="s">
+      <c r="AL3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="28"/>
+      <c r="AM3" s="26"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="21">
         <v>45597</v>
       </c>
@@ -3986,8 +4079,8 @@
       <c r="AI4" s="21">
         <v>45626</v>
       </c>
-      <c r="AJ4" s="26"/>
-      <c r="AK4" s="26"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -4012,72 +4105,78 @@
         <v>20</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G5" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="M5" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="N5" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="H5" s="32" t="s">
-        <v>132</v>
-      </c>
-      <c r="I5" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N5" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="O5" s="32" t="s">
-        <v>132</v>
+      <c r="O5" s="31" t="s">
+        <v>131</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="32" t="s">
-        <v>132</v>
+        <v>125</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V5" s="31" t="s">
+        <v>131</v>
       </c>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
-      <c r="Y5" s="35"/>
+      <c r="Y5" s="24"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
-      <c r="AC5" s="32" t="s">
-        <v>132</v>
+      <c r="AC5" s="31" t="s">
+        <v>131</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
-      <c r="AF5" s="35"/>
+      <c r="AF5" s="24"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
       <c r="AI5" s="11"/>
       <c r="AJ5" s="5">
-        <f>COUNTIF(F5:AI5,"P")</f>
-        <v>9</v>
+        <f t="shared" ref="AJ5:AJ36" si="1">COUNTIF(F5:AI5,"P")</f>
+        <v>11</v>
       </c>
       <c r="AK5" s="5">
-        <f>COUNTIF(F5:AI5,"A")</f>
-        <v>1</v>
+        <f t="shared" ref="AK5:AK36" si="2">COUNTIF(F5:AI5,"A")</f>
+        <v>2</v>
       </c>
       <c r="AL5" s="5" t="s">
         <v>8</v>
@@ -4105,62 +4204,68 @@
         <v>20</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H6" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H6" s="32"/>
       <c r="I6" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N6" s="40"/>
-      <c r="O6" s="33"/>
+      <c r="O6" s="32"/>
       <c r="P6" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R6" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V6" s="32"/>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
-      <c r="Y6" s="35"/>
+      <c r="Y6" s="24"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="11"/>
-      <c r="AC6" s="33"/>
+      <c r="AC6" s="32"/>
       <c r="AD6" s="11"/>
       <c r="AE6" s="11"/>
-      <c r="AF6" s="35"/>
+      <c r="AF6" s="24"/>
       <c r="AG6" s="11"/>
       <c r="AH6" s="11"/>
       <c r="AI6" s="11"/>
       <c r="AJ6" s="5">
-        <f>COUNTIF(F6:AI6,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK6" s="5">
-        <f>COUNTIF(F6:AI6,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="AL6" s="5" t="s">
         <v>10</v>
@@ -4177,70 +4282,76 @@
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>130</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>131</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H7" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H7" s="32"/>
       <c r="I7" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N7" s="40"/>
-      <c r="O7" s="33"/>
+      <c r="O7" s="32"/>
       <c r="P7" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R7" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V7" s="32"/>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
-      <c r="Y7" s="35"/>
+      <c r="Y7" s="24"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="11"/>
       <c r="AB7" s="11"/>
-      <c r="AC7" s="33"/>
+      <c r="AC7" s="32"/>
       <c r="AD7" s="11"/>
       <c r="AE7" s="11"/>
-      <c r="AF7" s="35"/>
+      <c r="AF7" s="24"/>
       <c r="AG7" s="11"/>
       <c r="AH7" s="11"/>
       <c r="AI7" s="11"/>
       <c r="AJ7" s="5">
-        <f>COUNTIF(F7:AI7,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK7" s="5">
-        <f>COUNTIF(F7:AI7,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL7" s="3"/>
@@ -4263,69 +4374,75 @@
         <v>20</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H8" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H8" s="32"/>
       <c r="I8" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N8" s="40"/>
-      <c r="O8" s="33"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R8" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V8" s="32"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
-      <c r="Y8" s="35"/>
+      <c r="Y8" s="24"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="11"/>
       <c r="AB8" s="11"/>
-      <c r="AC8" s="33"/>
+      <c r="AC8" s="32"/>
       <c r="AD8" s="11"/>
       <c r="AE8" s="11"/>
-      <c r="AF8" s="35"/>
+      <c r="AF8" s="24"/>
       <c r="AG8" s="11"/>
       <c r="AH8" s="11"/>
       <c r="AI8" s="11"/>
       <c r="AJ8" s="5">
-        <f>COUNTIF(F8:AI8,"P")</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="AK8" s="5">
-        <f>COUNTIF(F8:AI8,"A")</f>
-        <v>4</v>
-      </c>
-      <c r="AL8" s="27" t="s">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AL8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="28"/>
-      <c r="AN8" s="28"/>
-      <c r="AO8" s="29"/>
+      <c r="AM8" s="26"/>
+      <c r="AN8" s="26"/>
+      <c r="AO8" s="27"/>
     </row>
     <row r="9" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -4342,62 +4459,68 @@
         <v>20</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H9" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H9" s="32"/>
       <c r="I9" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M9" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N9" s="40"/>
-      <c r="O9" s="33"/>
+      <c r="O9" s="32"/>
       <c r="P9" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R9" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="S9" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="T9" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V9" s="32"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
-      <c r="Y9" s="35"/>
+      <c r="Y9" s="24"/>
       <c r="Z9" s="11"/>
       <c r="AA9" s="11"/>
       <c r="AB9" s="11"/>
-      <c r="AC9" s="33"/>
+      <c r="AC9" s="32"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
-      <c r="AF9" s="35"/>
+      <c r="AF9" s="24"/>
       <c r="AG9" s="11"/>
       <c r="AH9" s="11"/>
       <c r="AI9" s="11"/>
       <c r="AJ9" s="5">
-        <f>COUNTIF(F9:AI9,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="AK9" s="5">
-        <f>COUNTIF(F9:AI9,"A")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="AL9" s="5" t="s">
         <v>12</v>
@@ -4427,61 +4550,67 @@
         <v>20</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H10" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H10" s="32"/>
       <c r="I10" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M10" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N10" s="40"/>
-      <c r="O10" s="33"/>
+      <c r="O10" s="32"/>
       <c r="P10" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V10" s="32"/>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
-      <c r="Y10" s="35"/>
+      <c r="Y10" s="24"/>
       <c r="Z10" s="11"/>
       <c r="AA10" s="11"/>
       <c r="AB10" s="11"/>
-      <c r="AC10" s="33"/>
+      <c r="AC10" s="32"/>
       <c r="AD10" s="11"/>
       <c r="AE10" s="11"/>
-      <c r="AF10" s="35"/>
+      <c r="AF10" s="24"/>
       <c r="AG10" s="11"/>
       <c r="AH10" s="11"/>
       <c r="AI10" s="11"/>
       <c r="AJ10" s="5">
-        <f>COUNTIF(F10:AI10,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK10" s="5">
-        <f>COUNTIF(F10:AI10,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL10" s="5" t="s">
@@ -4515,61 +4644,67 @@
         <v>20</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H11" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H11" s="32"/>
       <c r="I11" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M11" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N11" s="40"/>
-      <c r="O11" s="33"/>
+      <c r="O11" s="32"/>
       <c r="P11" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q11" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R11" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V11" s="32"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
-      <c r="Y11" s="35"/>
+      <c r="Y11" s="24"/>
       <c r="Z11" s="11"/>
       <c r="AA11" s="11"/>
       <c r="AB11" s="11"/>
-      <c r="AC11" s="33"/>
+      <c r="AC11" s="32"/>
       <c r="AD11" s="11"/>
       <c r="AE11" s="11"/>
-      <c r="AF11" s="35"/>
+      <c r="AF11" s="24"/>
       <c r="AG11" s="11"/>
       <c r="AH11" s="11"/>
       <c r="AI11" s="11"/>
       <c r="AJ11" s="5">
-        <f>COUNTIF(F11:AI11,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK11" s="5">
-        <f>COUNTIF(F11:AI11,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="AL11" s="5" t="s">
@@ -4577,15 +4712,15 @@
       </c>
       <c r="AM11" s="12">
         <f>+AJ7+AJ18</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AN11" s="12">
         <f>AJ5+AJ6+AJ8+AJ9+AJ10+AJ11+AJ12+AJ13+AJ14+AJ15+AJ16+AJ17+AJ19+AJ20</f>
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="AO11" s="12">
         <f>AM11+AN11</f>
-        <v>136</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -4603,77 +4738,83 @@
         <v>20</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H12" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H12" s="32"/>
       <c r="I12" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N12" s="40"/>
-      <c r="O12" s="33"/>
+      <c r="O12" s="32"/>
       <c r="P12" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R12" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="S12" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V12" s="32"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
-      <c r="Y12" s="35"/>
+      <c r="Y12" s="24"/>
       <c r="Z12" s="11"/>
       <c r="AA12" s="11"/>
       <c r="AB12" s="11"/>
-      <c r="AC12" s="33"/>
+      <c r="AC12" s="32"/>
       <c r="AD12" s="11"/>
       <c r="AE12" s="11"/>
-      <c r="AF12" s="35"/>
+      <c r="AF12" s="24"/>
       <c r="AG12" s="11"/>
       <c r="AH12" s="11"/>
       <c r="AI12" s="11"/>
       <c r="AJ12" s="5">
-        <f>COUNTIF(F12:AI12,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="AK12" s="5">
-        <f>COUNTIF(F12:AI12,"A")</f>
-        <v>3</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="AL12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="AM12" s="12">
         <f>AM11/AM10</f>
-        <v>4.048582995951417E-2</v>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="AN12" s="12">
         <f>AN11/AN10</f>
-        <v>0.21245421245421245</v>
+        <v>0.27289377289377287</v>
       </c>
       <c r="AO12" s="12">
         <f>AO11/AO10</f>
-        <v>0.13076923076923078</v>
+        <v>0.16826923076923078</v>
       </c>
     </row>
     <row r="13" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -4691,61 +4832,67 @@
         <v>20</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H13" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H13" s="32"/>
       <c r="I13" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M13" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N13" s="40"/>
-      <c r="O13" s="33"/>
+      <c r="O13" s="32"/>
       <c r="P13" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R13" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V13" s="32"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
-      <c r="Y13" s="35"/>
+      <c r="Y13" s="24"/>
       <c r="Z13" s="11"/>
       <c r="AA13" s="11"/>
       <c r="AB13" s="11"/>
-      <c r="AC13" s="33"/>
+      <c r="AC13" s="32"/>
       <c r="AD13" s="11"/>
       <c r="AE13" s="11"/>
-      <c r="AF13" s="35"/>
+      <c r="AF13" s="24"/>
       <c r="AG13" s="11"/>
       <c r="AH13" s="11"/>
       <c r="AI13" s="11"/>
       <c r="AJ13" s="5">
-        <f>COUNTIF(F13:AI13,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK13" s="5">
-        <f>COUNTIF(F13:AI13,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL13" s="3"/>
@@ -4768,61 +4915,67 @@
         <v>20</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H14" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H14" s="32"/>
       <c r="I14" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K14" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M14" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N14" s="40"/>
-      <c r="O14" s="33"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R14" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V14" s="32"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
-      <c r="Y14" s="35"/>
+      <c r="Y14" s="24"/>
       <c r="Z14" s="11"/>
       <c r="AA14" s="11"/>
       <c r="AB14" s="11"/>
-      <c r="AC14" s="33"/>
+      <c r="AC14" s="32"/>
       <c r="AD14" s="11"/>
       <c r="AE14" s="11"/>
-      <c r="AF14" s="35"/>
+      <c r="AF14" s="24"/>
       <c r="AG14" s="11"/>
       <c r="AH14" s="11"/>
       <c r="AI14" s="11"/>
       <c r="AJ14" s="5">
-        <f>COUNTIF(F14:AI14,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK14" s="5">
-        <f>COUNTIF(F14:AI14,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL14" s="19"/>
@@ -4845,62 +4998,68 @@
         <v>20</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H15" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H15" s="32"/>
       <c r="I15" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N15" s="40"/>
-      <c r="O15" s="33"/>
+      <c r="O15" s="32"/>
       <c r="P15" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V15" s="32"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
-      <c r="Y15" s="35"/>
+      <c r="Y15" s="24"/>
       <c r="Z15" s="11"/>
       <c r="AA15" s="11"/>
       <c r="AB15" s="11"/>
-      <c r="AC15" s="33"/>
+      <c r="AC15" s="32"/>
       <c r="AD15" s="11"/>
       <c r="AE15" s="11"/>
-      <c r="AF15" s="35"/>
+      <c r="AF15" s="24"/>
       <c r="AG15" s="11"/>
       <c r="AH15" s="11"/>
       <c r="AI15" s="11"/>
       <c r="AJ15" s="5">
-        <f>COUNTIF(F15:AI15,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK15" s="5">
-        <f>COUNTIF(F15:AI15,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
@@ -4922,69 +5081,75 @@
         <v>20</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H16" s="32"/>
       <c r="I16" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M16" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N16" s="40"/>
-      <c r="O16" s="33"/>
+      <c r="O16" s="32"/>
       <c r="P16" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q16" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V16" s="32"/>
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
-      <c r="Y16" s="35"/>
+      <c r="Y16" s="24"/>
       <c r="Z16" s="11"/>
       <c r="AA16" s="11"/>
       <c r="AB16" s="11"/>
-      <c r="AC16" s="33"/>
+      <c r="AC16" s="32"/>
       <c r="AD16" s="11"/>
       <c r="AE16" s="11"/>
-      <c r="AF16" s="35"/>
+      <c r="AF16" s="24"/>
       <c r="AG16" s="11"/>
       <c r="AH16" s="11"/>
       <c r="AI16" s="11"/>
       <c r="AJ16" s="5">
-        <f>COUNTIF(F16:AI16,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK16" s="5">
-        <f>COUNTIF(F16:AI16,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AL16" s="27" t="s">
+      <c r="AL16" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="28"/>
-      <c r="AN16" s="28"/>
-      <c r="AO16" s="29"/>
+      <c r="AM16" s="26"/>
+      <c r="AN16" s="26"/>
+      <c r="AO16" s="27"/>
     </row>
     <row r="17" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -5001,62 +5166,68 @@
         <v>20</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H17" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H17" s="32"/>
       <c r="I17" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M17" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N17" s="40"/>
-      <c r="O17" s="33"/>
+      <c r="O17" s="32"/>
       <c r="P17" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q17" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R17" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="S17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="T17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V17" s="32"/>
       <c r="W17" s="11"/>
       <c r="X17" s="11"/>
-      <c r="Y17" s="35"/>
+      <c r="Y17" s="24"/>
       <c r="Z17" s="11"/>
       <c r="AA17" s="11"/>
       <c r="AB17" s="11"/>
-      <c r="AC17" s="33"/>
+      <c r="AC17" s="32"/>
       <c r="AD17" s="11"/>
       <c r="AE17" s="11"/>
-      <c r="AF17" s="35"/>
+      <c r="AF17" s="24"/>
       <c r="AG17" s="11"/>
       <c r="AH17" s="11"/>
       <c r="AI17" s="11"/>
       <c r="AJ17" s="5">
-        <f>COUNTIF(F17:AI17,"P")</f>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="AK17" s="5">
-        <f>COUNTIF(F17:AI17,"A")</f>
-        <v>8</v>
+        <f t="shared" si="2"/>
+        <v>9</v>
       </c>
       <c r="AL17" s="5" t="s">
         <v>12</v>
@@ -5086,61 +5257,67 @@
         <v>20</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H18" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H18" s="32"/>
       <c r="I18" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M18" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N18" s="40"/>
-      <c r="O18" s="33"/>
+      <c r="O18" s="32"/>
       <c r="P18" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R18" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V18" s="32"/>
       <c r="W18" s="11"/>
       <c r="X18" s="11"/>
-      <c r="Y18" s="35"/>
+      <c r="Y18" s="24"/>
       <c r="Z18" s="11"/>
       <c r="AA18" s="11"/>
       <c r="AB18" s="11"/>
-      <c r="AC18" s="33"/>
+      <c r="AC18" s="32"/>
       <c r="AD18" s="11"/>
       <c r="AE18" s="11"/>
-      <c r="AF18" s="35"/>
+      <c r="AF18" s="24"/>
       <c r="AG18" s="11"/>
       <c r="AH18" s="11"/>
       <c r="AI18" s="11"/>
       <c r="AJ18" s="5">
-        <f>COUNTIF(F18:AI18,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK18" s="5">
-        <f>COUNTIF(F18:AI18,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL18" s="5" t="s">
@@ -5174,61 +5351,67 @@
         <v>20</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H19" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H19" s="32"/>
       <c r="I19" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M19" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N19" s="40"/>
-      <c r="O19" s="33"/>
+      <c r="O19" s="32"/>
       <c r="P19" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V19" s="32"/>
       <c r="W19" s="11"/>
       <c r="X19" s="11"/>
-      <c r="Y19" s="35"/>
+      <c r="Y19" s="24"/>
       <c r="Z19" s="11"/>
       <c r="AA19" s="11"/>
       <c r="AB19" s="11"/>
-      <c r="AC19" s="33"/>
+      <c r="AC19" s="32"/>
       <c r="AD19" s="11"/>
       <c r="AE19" s="11"/>
-      <c r="AF19" s="35"/>
+      <c r="AF19" s="24"/>
       <c r="AG19" s="11"/>
       <c r="AH19" s="11"/>
       <c r="AI19" s="11"/>
       <c r="AJ19" s="5">
-        <f>COUNTIF(F19:AI19,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK19" s="5">
-        <f>COUNTIF(F19:AI19,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL19" s="5" t="s">
@@ -5236,15 +5419,15 @@
       </c>
       <c r="AM19" s="12">
         <f>AM18-AM11</f>
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="AN19" s="12">
         <f>AN18-AN11</f>
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="AO19" s="12">
         <f>AM19+AN19</f>
-        <v>904</v>
+        <v>865</v>
       </c>
     </row>
     <row r="20" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5262,61 +5445,67 @@
         <v>20</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H20" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H20" s="32"/>
       <c r="I20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N20" s="40"/>
-      <c r="O20" s="33"/>
+      <c r="O20" s="32"/>
       <c r="P20" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V20" s="32"/>
       <c r="W20" s="11"/>
       <c r="X20" s="11"/>
-      <c r="Y20" s="35"/>
+      <c r="Y20" s="24"/>
       <c r="Z20" s="11"/>
       <c r="AA20" s="11"/>
       <c r="AB20" s="11"/>
-      <c r="AC20" s="33"/>
+      <c r="AC20" s="32"/>
       <c r="AD20" s="11"/>
       <c r="AE20" s="11"/>
-      <c r="AF20" s="35"/>
+      <c r="AF20" s="24"/>
       <c r="AG20" s="11"/>
       <c r="AH20" s="11"/>
       <c r="AI20" s="11"/>
       <c r="AJ20" s="5">
-        <f>COUNTIF(F20:AI20,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK20" s="5">
-        <f>COUNTIF(F20:AI20,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL20" s="5" t="s">
@@ -5324,15 +5513,15 @@
       </c>
       <c r="AM20" s="20">
         <f>AM19/AM18</f>
-        <v>0.95951417004048578</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="AN20" s="20">
         <f>AN19/AN18</f>
-        <v>0.78754578754578752</v>
+        <v>0.72710622710622708</v>
       </c>
       <c r="AO20" s="20">
         <f>AO19/AO18</f>
-        <v>0.86923076923076925</v>
+        <v>0.83173076923076927</v>
       </c>
     </row>
     <row r="21" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5350,61 +5539,67 @@
         <v>20</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H21" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H21" s="32"/>
       <c r="I21" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M21" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N21" s="40"/>
-      <c r="O21" s="33"/>
+      <c r="O21" s="32"/>
       <c r="P21" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q21" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V21" s="32"/>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
-      <c r="Y21" s="35"/>
+      <c r="Y21" s="24"/>
       <c r="Z21" s="11"/>
       <c r="AA21" s="11"/>
       <c r="AB21" s="11"/>
-      <c r="AC21" s="33"/>
+      <c r="AC21" s="32"/>
       <c r="AD21" s="11"/>
       <c r="AE21" s="11"/>
-      <c r="AF21" s="35"/>
+      <c r="AF21" s="24"/>
       <c r="AG21" s="11"/>
       <c r="AH21" s="11"/>
       <c r="AI21" s="11"/>
       <c r="AJ21" s="5">
-        <f>COUNTIF(F21:AI21,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK21" s="5">
-        <f>COUNTIF(F21:AI21,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -5423,61 +5618,67 @@
         <v>20</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H22" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H22" s="32"/>
       <c r="I22" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M22" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N22" s="40"/>
-      <c r="O22" s="33"/>
+      <c r="O22" s="32"/>
       <c r="P22" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R22" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V22" s="32"/>
       <c r="W22" s="11"/>
       <c r="X22" s="11"/>
-      <c r="Y22" s="35"/>
+      <c r="Y22" s="24"/>
       <c r="Z22" s="11"/>
       <c r="AA22" s="11"/>
       <c r="AB22" s="11"/>
-      <c r="AC22" s="33"/>
+      <c r="AC22" s="32"/>
       <c r="AD22" s="11"/>
       <c r="AE22" s="11"/>
-      <c r="AF22" s="35"/>
+      <c r="AF22" s="24"/>
       <c r="AG22" s="11"/>
       <c r="AH22" s="11"/>
       <c r="AI22" s="11"/>
       <c r="AJ22" s="5">
-        <f>COUNTIF(F22:AI22,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK22" s="5">
-        <f>COUNTIF(F22:AI22,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5496,61 +5697,67 @@
         <v>20</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H23" s="32"/>
       <c r="I23" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M23" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N23" s="40"/>
-      <c r="O23" s="33"/>
+      <c r="O23" s="32"/>
       <c r="P23" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q23" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S23" s="11"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V23" s="32"/>
       <c r="W23" s="11"/>
       <c r="X23" s="11"/>
-      <c r="Y23" s="35"/>
+      <c r="Y23" s="24"/>
       <c r="Z23" s="11"/>
       <c r="AA23" s="11"/>
       <c r="AB23" s="11"/>
-      <c r="AC23" s="33"/>
+      <c r="AC23" s="32"/>
       <c r="AD23" s="11"/>
       <c r="AE23" s="11"/>
-      <c r="AF23" s="35"/>
+      <c r="AF23" s="24"/>
       <c r="AG23" s="11"/>
       <c r="AH23" s="11"/>
       <c r="AI23" s="11"/>
       <c r="AJ23" s="5">
-        <f>COUNTIF(F23:AI23,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK23" s="5">
-        <f>COUNTIF(F23:AI23,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5569,61 +5776,67 @@
         <v>20</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H24" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H24" s="32"/>
       <c r="I24" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M24" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N24" s="40"/>
-      <c r="O24" s="33"/>
+      <c r="O24" s="32"/>
       <c r="P24" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q24" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V24" s="32"/>
       <c r="W24" s="11"/>
       <c r="X24" s="11"/>
-      <c r="Y24" s="35"/>
+      <c r="Y24" s="24"/>
       <c r="Z24" s="11"/>
       <c r="AA24" s="11"/>
       <c r="AB24" s="11"/>
-      <c r="AC24" s="33"/>
+      <c r="AC24" s="32"/>
       <c r="AD24" s="11"/>
       <c r="AE24" s="11"/>
-      <c r="AF24" s="35"/>
+      <c r="AF24" s="24"/>
       <c r="AG24" s="11"/>
       <c r="AH24" s="11"/>
       <c r="AI24" s="11"/>
       <c r="AJ24" s="5">
-        <f>COUNTIF(F24:AI24,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK24" s="5">
-        <f>COUNTIF(F24:AI24,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -5642,62 +5855,68 @@
         <v>20</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H25" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H25" s="32"/>
       <c r="I25" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M25" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N25" s="40"/>
-      <c r="O25" s="33"/>
+      <c r="O25" s="32"/>
       <c r="P25" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q25" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V25" s="32"/>
       <c r="W25" s="11"/>
       <c r="X25" s="11"/>
-      <c r="Y25" s="35"/>
+      <c r="Y25" s="24"/>
       <c r="Z25" s="11"/>
       <c r="AA25" s="11"/>
       <c r="AB25" s="11"/>
-      <c r="AC25" s="33"/>
+      <c r="AC25" s="32"/>
       <c r="AD25" s="11"/>
       <c r="AE25" s="11"/>
-      <c r="AF25" s="35"/>
+      <c r="AF25" s="24"/>
       <c r="AG25" s="11"/>
       <c r="AH25" s="11"/>
       <c r="AI25" s="11"/>
       <c r="AJ25" s="5">
-        <f>COUNTIF(F25:AI25,"P")</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="AK25" s="5">
-        <f>COUNTIF(F25:AI25,"A")</f>
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5715,62 +5934,68 @@
         <v>20</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H26" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H26" s="32"/>
       <c r="I26" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M26" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N26" s="40"/>
-      <c r="O26" s="33"/>
+      <c r="O26" s="32"/>
       <c r="P26" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S26" s="11"/>
-      <c r="T26" s="11"/>
-      <c r="U26" s="11"/>
-      <c r="V26" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="T26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V26" s="32"/>
       <c r="W26" s="11"/>
       <c r="X26" s="11"/>
-      <c r="Y26" s="35"/>
+      <c r="Y26" s="24"/>
       <c r="Z26" s="11"/>
       <c r="AA26" s="11"/>
       <c r="AB26" s="11"/>
-      <c r="AC26" s="33"/>
+      <c r="AC26" s="32"/>
       <c r="AD26" s="11"/>
       <c r="AE26" s="11"/>
-      <c r="AF26" s="35"/>
+      <c r="AF26" s="24"/>
       <c r="AG26" s="11"/>
       <c r="AH26" s="11"/>
       <c r="AI26" s="11"/>
       <c r="AJ26" s="5">
-        <f>COUNTIF(F26:AI26,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK26" s="5">
-        <f>COUNTIF(F26:AI26,"A")</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5788,61 +6013,67 @@
         <v>20</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H27" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H27" s="32"/>
       <c r="I27" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M27" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N27" s="40"/>
-      <c r="O27" s="33"/>
+      <c r="O27" s="32"/>
       <c r="P27" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S27" s="11"/>
-      <c r="T27" s="11"/>
-      <c r="U27" s="11"/>
-      <c r="V27" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V27" s="32"/>
       <c r="W27" s="11"/>
       <c r="X27" s="11"/>
-      <c r="Y27" s="35"/>
+      <c r="Y27" s="24"/>
       <c r="Z27" s="11"/>
       <c r="AA27" s="11"/>
       <c r="AB27" s="11"/>
-      <c r="AC27" s="33"/>
+      <c r="AC27" s="32"/>
       <c r="AD27" s="11"/>
       <c r="AE27" s="11"/>
-      <c r="AF27" s="35"/>
+      <c r="AF27" s="24"/>
       <c r="AG27" s="11"/>
       <c r="AH27" s="11"/>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="5">
-        <f>COUNTIF(F27:AI27,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK27" s="5">
-        <f>COUNTIF(F27:AI27,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -5861,62 +6092,68 @@
         <v>20</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H28" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H28" s="32"/>
       <c r="I28" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J28" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M28" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N28" s="40"/>
-      <c r="O28" s="33"/>
+      <c r="O28" s="32"/>
       <c r="P28" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S28" s="11"/>
-      <c r="T28" s="11"/>
-      <c r="U28" s="11"/>
-      <c r="V28" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U28" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V28" s="32"/>
       <c r="W28" s="11"/>
       <c r="X28" s="11"/>
-      <c r="Y28" s="35"/>
+      <c r="Y28" s="24"/>
       <c r="Z28" s="11"/>
       <c r="AA28" s="11"/>
       <c r="AB28" s="11"/>
-      <c r="AC28" s="33"/>
+      <c r="AC28" s="32"/>
       <c r="AD28" s="11"/>
       <c r="AE28" s="11"/>
-      <c r="AF28" s="35"/>
+      <c r="AF28" s="24"/>
       <c r="AG28" s="11"/>
       <c r="AH28" s="11"/>
       <c r="AI28" s="11"/>
       <c r="AJ28" s="5">
-        <f>COUNTIF(F28:AI28,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK28" s="5">
-        <f>COUNTIF(F28:AI28,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5934,61 +6171,67 @@
         <v>20</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H29" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H29" s="32"/>
       <c r="I29" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J29" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K29" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L29" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M29" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N29" s="40"/>
-      <c r="O29" s="33"/>
+      <c r="O29" s="32"/>
       <c r="P29" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q29" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R29" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S29" s="11"/>
-      <c r="T29" s="11"/>
-      <c r="U29" s="11"/>
-      <c r="V29" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V29" s="32"/>
       <c r="W29" s="11"/>
       <c r="X29" s="11"/>
-      <c r="Y29" s="35"/>
+      <c r="Y29" s="24"/>
       <c r="Z29" s="11"/>
       <c r="AA29" s="11"/>
       <c r="AB29" s="11"/>
-      <c r="AC29" s="33"/>
+      <c r="AC29" s="32"/>
       <c r="AD29" s="11"/>
       <c r="AE29" s="11"/>
-      <c r="AF29" s="35"/>
+      <c r="AF29" s="24"/>
       <c r="AG29" s="11"/>
       <c r="AH29" s="11"/>
       <c r="AI29" s="11"/>
       <c r="AJ29" s="5">
-        <f>COUNTIF(F29:AI29,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK29" s="5">
-        <f>COUNTIF(F29:AI29,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6007,62 +6250,68 @@
         <v>20</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H30" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H30" s="32"/>
       <c r="I30" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K30" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L30" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M30" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N30" s="40"/>
-      <c r="O30" s="33"/>
+      <c r="O30" s="32"/>
       <c r="P30" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q30" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S30" s="11"/>
-      <c r="T30" s="11"/>
-      <c r="U30" s="11"/>
-      <c r="V30" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U30" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V30" s="32"/>
       <c r="W30" s="11"/>
       <c r="X30" s="11"/>
-      <c r="Y30" s="35"/>
+      <c r="Y30" s="24"/>
       <c r="Z30" s="11"/>
       <c r="AA30" s="11"/>
       <c r="AB30" s="11"/>
-      <c r="AC30" s="33"/>
+      <c r="AC30" s="32"/>
       <c r="AD30" s="11"/>
       <c r="AE30" s="11"/>
-      <c r="AF30" s="35"/>
+      <c r="AF30" s="24"/>
       <c r="AG30" s="11"/>
       <c r="AH30" s="11"/>
       <c r="AI30" s="11"/>
       <c r="AJ30" s="5">
-        <f>COUNTIF(F30:AI30,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK30" s="5">
-        <f>COUNTIF(F30:AI30,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -6080,61 +6329,67 @@
         <v>20</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H31" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H31" s="32"/>
       <c r="I31" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J31" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K31" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L31" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M31" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N31" s="40"/>
-      <c r="O31" s="33"/>
+      <c r="O31" s="32"/>
       <c r="P31" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R31" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S31" s="11"/>
-      <c r="T31" s="11"/>
-      <c r="U31" s="11"/>
-      <c r="V31" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V31" s="32"/>
       <c r="W31" s="11"/>
       <c r="X31" s="11"/>
-      <c r="Y31" s="35"/>
+      <c r="Y31" s="24"/>
       <c r="Z31" s="11"/>
       <c r="AA31" s="11"/>
       <c r="AB31" s="11"/>
-      <c r="AC31" s="33"/>
+      <c r="AC31" s="32"/>
       <c r="AD31" s="11"/>
       <c r="AE31" s="11"/>
-      <c r="AF31" s="35"/>
+      <c r="AF31" s="24"/>
       <c r="AG31" s="11"/>
       <c r="AH31" s="11"/>
       <c r="AI31" s="11"/>
       <c r="AJ31" s="5">
-        <f>COUNTIF(F31:AI31,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK31" s="5">
-        <f>COUNTIF(F31:AI31,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6153,62 +6408,68 @@
         <v>20</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H32" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="H32" s="32"/>
       <c r="I32" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K32" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L32" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M32" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N32" s="40"/>
-      <c r="O32" s="33"/>
+      <c r="O32" s="32"/>
       <c r="P32" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S32" s="11"/>
-      <c r="T32" s="11"/>
-      <c r="U32" s="11"/>
-      <c r="V32" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T32" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V32" s="32"/>
       <c r="W32" s="11"/>
       <c r="X32" s="11"/>
-      <c r="Y32" s="35"/>
+      <c r="Y32" s="24"/>
       <c r="Z32" s="11"/>
       <c r="AA32" s="11"/>
       <c r="AB32" s="11"/>
-      <c r="AC32" s="33"/>
+      <c r="AC32" s="32"/>
       <c r="AD32" s="11"/>
       <c r="AE32" s="11"/>
-      <c r="AF32" s="35"/>
+      <c r="AF32" s="24"/>
       <c r="AG32" s="11"/>
       <c r="AH32" s="11"/>
       <c r="AI32" s="11"/>
       <c r="AJ32" s="5">
-        <f>COUNTIF(F32:AI32,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="AK32" s="5">
-        <f>COUNTIF(F32:AI32,"A")</f>
-        <v>3</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:37" ht="16.5" x14ac:dyDescent="0.25">
@@ -6226,61 +6487,67 @@
         <v>20</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H33" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H33" s="32"/>
       <c r="I33" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K33" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L33" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M33" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N33" s="40"/>
-      <c r="O33" s="33"/>
+      <c r="O33" s="32"/>
       <c r="P33" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S33" s="11"/>
-      <c r="T33" s="11"/>
-      <c r="U33" s="11"/>
-      <c r="V33" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V33" s="32"/>
       <c r="W33" s="11"/>
       <c r="X33" s="11"/>
-      <c r="Y33" s="35"/>
+      <c r="Y33" s="24"/>
       <c r="Z33" s="11"/>
       <c r="AA33" s="11"/>
       <c r="AB33" s="11"/>
-      <c r="AC33" s="33"/>
+      <c r="AC33" s="32"/>
       <c r="AD33" s="11"/>
       <c r="AE33" s="11"/>
-      <c r="AF33" s="35"/>
+      <c r="AF33" s="24"/>
       <c r="AG33" s="11"/>
       <c r="AH33" s="11"/>
       <c r="AI33" s="11"/>
       <c r="AJ33" s="5">
-        <f>COUNTIF(F33:AI33,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK33" s="5">
-        <f>COUNTIF(F33:AI33,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6299,61 +6566,67 @@
         <v>20</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H34" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H34" s="32"/>
       <c r="I34" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J34" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K34" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L34" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M34" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N34" s="40"/>
-      <c r="O34" s="33"/>
+      <c r="O34" s="32"/>
       <c r="P34" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q34" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R34" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S34" s="11"/>
-      <c r="T34" s="11"/>
-      <c r="U34" s="11"/>
-      <c r="V34" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="U34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V34" s="32"/>
       <c r="W34" s="11"/>
       <c r="X34" s="11"/>
-      <c r="Y34" s="35"/>
+      <c r="Y34" s="24"/>
       <c r="Z34" s="11"/>
       <c r="AA34" s="11"/>
       <c r="AB34" s="11"/>
-      <c r="AC34" s="33"/>
+      <c r="AC34" s="32"/>
       <c r="AD34" s="11"/>
       <c r="AE34" s="11"/>
-      <c r="AF34" s="35"/>
+      <c r="AF34" s="24"/>
       <c r="AG34" s="11"/>
       <c r="AH34" s="11"/>
       <c r="AI34" s="11"/>
       <c r="AJ34" s="5">
-        <f>COUNTIF(F34:AI34,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="AK34" s="5">
-        <f>COUNTIF(F34:AI34,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -6372,62 +6645,68 @@
         <v>20</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H35" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="H35" s="32"/>
       <c r="I35" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J35" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K35" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L35" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M35" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N35" s="40"/>
-      <c r="O35" s="33"/>
+      <c r="O35" s="32"/>
       <c r="P35" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q35" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R35" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S35" s="11"/>
-      <c r="T35" s="11"/>
-      <c r="U35" s="11"/>
-      <c r="V35" s="33"/>
+        <v>125</v>
+      </c>
+      <c r="S35" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V35" s="32"/>
       <c r="W35" s="11"/>
       <c r="X35" s="11"/>
-      <c r="Y35" s="35"/>
+      <c r="Y35" s="24"/>
       <c r="Z35" s="11"/>
       <c r="AA35" s="11"/>
       <c r="AB35" s="11"/>
-      <c r="AC35" s="33"/>
+      <c r="AC35" s="32"/>
       <c r="AD35" s="11"/>
       <c r="AE35" s="11"/>
-      <c r="AF35" s="35"/>
+      <c r="AF35" s="24"/>
       <c r="AG35" s="11"/>
       <c r="AH35" s="11"/>
       <c r="AI35" s="11"/>
       <c r="AJ35" s="5">
-        <f>COUNTIF(F35:AI35,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK35" s="5">
-        <f>COUNTIF(F35:AI35,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="16.5" x14ac:dyDescent="0.25">
@@ -6445,76 +6724,72 @@
         <v>20</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H36" s="34"/>
+        <v>125</v>
+      </c>
+      <c r="H36" s="33"/>
       <c r="I36" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J36" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K36" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L36" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M36" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N36" s="41"/>
-      <c r="O36" s="34"/>
+      <c r="O36" s="33"/>
       <c r="P36" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q36" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R36" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="S36" s="11"/>
-      <c r="T36" s="11"/>
-      <c r="U36" s="11"/>
-      <c r="V36" s="34"/>
+        <v>125</v>
+      </c>
+      <c r="S36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="T36" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="U36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V36" s="33"/>
       <c r="W36" s="11"/>
       <c r="X36" s="11"/>
-      <c r="Y36" s="35"/>
+      <c r="Y36" s="24"/>
       <c r="Z36" s="11"/>
       <c r="AA36" s="11"/>
       <c r="AB36" s="11"/>
-      <c r="AC36" s="34"/>
+      <c r="AC36" s="33"/>
       <c r="AD36" s="11"/>
       <c r="AE36" s="11"/>
-      <c r="AF36" s="35"/>
+      <c r="AF36" s="24"/>
       <c r="AG36" s="11"/>
       <c r="AH36" s="11"/>
       <c r="AI36" s="11"/>
       <c r="AJ36" s="5">
-        <f>COUNTIF(F36:AI36,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="AK36" s="5">
-        <f>COUNTIF(F36:AI36,"A")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="H5:H36"/>
-    <mergeCell ref="N5:N36"/>
-    <mergeCell ref="O5:O36"/>
-    <mergeCell ref="V5:V36"/>
-    <mergeCell ref="AC5:AC36"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL16:AO16"/>
     <mergeCell ref="A2:AI2"/>
     <mergeCell ref="A1:AI1"/>
     <mergeCell ref="A3:A4"/>
@@ -6522,31 +6797,41 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="H5:H36"/>
+    <mergeCell ref="N5:N36"/>
+    <mergeCell ref="O5:O36"/>
+    <mergeCell ref="V5:V36"/>
+    <mergeCell ref="AC5:AC36"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z6:AB36 AL4:AM4 AL5:AL6 AM9:AO9 AL9:AL12 AM17:AO17 AL17:AL20 AG6:AI36 F6:G36 I6:M36 P6:U36 W6:X36 AD6:AE36 F3:AI5">
-    <cfRule type="expression" dxfId="11" priority="11">
+  <conditionalFormatting sqref="F3:AI4 F5:O5 V5 AC5 P5:U36 W5:AB36 AD5:AI36 F6:G36 I6:M36">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>F$4=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:AI5 F6:G36 I6:M36 P6:U36 W6:X36 Z6:AB36 AD6:AE36 AG6:AI36 AL4:AM4 AL5:AL6 AM9:AO9 AL9:AL12 AM17:AO17 AL17:AL20">
+    <cfRule type="expression" dxfId="4" priority="11">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z6:AB36 AG6:AI36 F6:G36 I6:M36 P6:U36 W6:X36 AD6:AE36 F5:AI5">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+  <conditionalFormatting sqref="F5:AI5 F6:G36 I6:M36 P6:U36 W6:X36 Z6:AB36 AD6:AE36 AG6:AI36">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AK3 AJ5:AK36">
-    <cfRule type="expression" dxfId="7" priority="12">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>#REF!="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AI4 F6:G36 I6:M36 P5:U36 F5:O5 W5:AB36 V5 AD5:AI36 AC5">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>F$4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Sindhi Muslim/Student Attendance/Class 1/Class 1 - Monthly Attendance - November-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/Class 1/Class 1 - Monthly Attendance - November-2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\Class 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C54913A-AA32-4A0C-B22B-7D3EE9E7CE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB166CA-0214-4EDF-897A-4309DEDB15F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="542" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="134">
   <si>
     <t>S.No</t>
   </si>
@@ -434,6 +434,9 @@
   </si>
   <si>
     <t>Monthly Attendence Month of November-2024</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -665,7 +668,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -717,9 +720,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1236,97 +1236,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="38"/>
-      <c r="AC1" s="38"/>
-      <c r="AD1" s="38"/>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="38"/>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="38"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="37"/>
-      <c r="AF2" s="37"/>
-      <c r="AG2" s="37"/>
-      <c r="AH2" s="37"/>
-      <c r="AI2" s="37"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="27" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1449,25 +1449,25 @@
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="AJ3" s="30" t="s">
+      <c r="AJ3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="30" t="s">
+      <c r="AK3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="25" t="s">
+      <c r="AL3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="26"/>
+      <c r="AM3" s="25"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
       <c r="F4" s="21">
         <v>45597</v>
       </c>
@@ -1558,8 +1558,8 @@
       <c r="AI4" s="21">
         <v>45626</v>
       </c>
-      <c r="AJ4" s="30"/>
-      <c r="AK4" s="30"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="29"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1589,7 +1589,7 @@
       <c r="G5" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="H5" s="30" t="s">
         <v>124</v>
       </c>
       <c r="I5" s="22" t="s">
@@ -1607,10 +1607,10 @@
       <c r="M5" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="N5" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="O5" s="31" t="s">
+      <c r="O5" s="30" t="s">
         <v>124</v>
       </c>
       <c r="P5" s="11" t="s">
@@ -1631,27 +1631,51 @@
       <c r="U5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V5" s="31" t="s">
+      <c r="V5" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="24"/>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="11"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="31" t="s">
+      <c r="W5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC5" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="11"/>
-      <c r="AF5" s="24"/>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="11"/>
+      <c r="AD5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI5" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ5" s="5">
         <f t="shared" ref="AJ5:AJ28" si="2">COUNTIF(F5:AI5,"P")</f>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK28" si="3">COUNTIF(F5:AI5,"A")</f>
@@ -1688,7 +1712,7 @@
       <c r="G6" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H6" s="32"/>
+      <c r="H6" s="31"/>
       <c r="I6" s="22" t="s">
         <v>126</v>
       </c>
@@ -1704,8 +1728,8 @@
       <c r="M6" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N6" s="35"/>
-      <c r="O6" s="32"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="31"/>
       <c r="P6" s="11" t="s">
         <v>126</v>
       </c>
@@ -1724,27 +1748,51 @@
       <c r="U6" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V6" s="32"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="24"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="11"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="11"/>
-      <c r="AE6" s="11"/>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="11"/>
-      <c r="AH6" s="11"/>
-      <c r="AI6" s="11"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI6" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="AJ6" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AL6" s="5" t="s">
         <v>10</v>
@@ -1775,7 +1823,7 @@
       <c r="G7" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H7" s="32"/>
+      <c r="H7" s="31"/>
       <c r="I7" s="22" t="s">
         <v>125</v>
       </c>
@@ -1791,8 +1839,8 @@
       <c r="M7" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N7" s="35"/>
-      <c r="O7" s="32"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="31"/>
       <c r="P7" s="11" t="s">
         <v>125</v>
       </c>
@@ -1811,23 +1859,47 @@
       <c r="U7" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V7" s="32"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="24"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="11"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="32"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="24"/>
-      <c r="AG7" s="11"/>
-      <c r="AH7" s="11"/>
-      <c r="AI7" s="11"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC7" s="31"/>
+      <c r="AD7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI7" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ7" s="5">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK7" s="5">
         <f t="shared" si="3"/>
@@ -1858,7 +1930,7 @@
       <c r="G8" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H8" s="32"/>
+      <c r="H8" s="31"/>
       <c r="I8" s="22" t="s">
         <v>125</v>
       </c>
@@ -1874,8 +1946,8 @@
       <c r="M8" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N8" s="35"/>
-      <c r="O8" s="32"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="31"/>
       <c r="P8" s="11" t="s">
         <v>125</v>
       </c>
@@ -1894,34 +1966,58 @@
       <c r="U8" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V8" s="32"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="11"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="32"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="11"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="11"/>
-      <c r="AH8" s="11"/>
-      <c r="AI8" s="11"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI8" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ8" s="5">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK8" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AL8" s="25" t="s">
+      <c r="AL8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="26"/>
-      <c r="AN8" s="26"/>
-      <c r="AO8" s="27"/>
+      <c r="AM8" s="25"/>
+      <c r="AN8" s="25"/>
+      <c r="AO8" s="26"/>
     </row>
     <row r="9" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -1943,7 +2039,7 @@
       <c r="G9" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H9" s="32"/>
+      <c r="H9" s="31"/>
       <c r="I9" s="22" t="s">
         <v>125</v>
       </c>
@@ -1959,8 +2055,8 @@
       <c r="M9" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N9" s="35"/>
-      <c r="O9" s="32"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="31"/>
       <c r="P9" s="11" t="s">
         <v>125</v>
       </c>
@@ -1979,27 +2075,51 @@
       <c r="U9" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V9" s="32"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="11"/>
-      <c r="AA9" s="11"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="32"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="24"/>
-      <c r="AG9" s="11"/>
-      <c r="AH9" s="11"/>
-      <c r="AI9" s="11"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X9" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB9" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI9" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ9" s="5">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AK9" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL9" s="5" t="s">
         <v>12</v>
@@ -2034,7 +2154,7 @@
       <c r="G10" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="31"/>
       <c r="I10" s="22" t="s">
         <v>126</v>
       </c>
@@ -2048,10 +2168,10 @@
         <v>125</v>
       </c>
       <c r="M10" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N10" s="35"/>
-      <c r="O10" s="32"/>
+        <v>125</v>
+      </c>
+      <c r="N10" s="34"/>
+      <c r="O10" s="31"/>
       <c r="P10" s="11" t="s">
         <v>125</v>
       </c>
@@ -2070,27 +2190,51 @@
       <c r="U10" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V10" s="32"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="11"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="32"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="24"/>
-      <c r="AG10" s="11"/>
-      <c r="AH10" s="11"/>
-      <c r="AI10" s="11"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z10" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB10" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH10" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI10" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ10" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL10" s="5" t="s">
         <v>16</v>
@@ -2128,7 +2272,7 @@
       <c r="G11" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="31"/>
       <c r="I11" s="22" t="s">
         <v>125</v>
       </c>
@@ -2144,8 +2288,8 @@
       <c r="M11" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N11" s="35"/>
-      <c r="O11" s="32"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="31"/>
       <c r="P11" s="11" t="s">
         <v>125</v>
       </c>
@@ -2164,23 +2308,47 @@
       <c r="U11" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V11" s="32"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="24"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="11"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="32"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="24"/>
-      <c r="AG11" s="11"/>
-      <c r="AH11" s="11"/>
-      <c r="AI11" s="11"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI11" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ11" s="5">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" si="3"/>
@@ -2191,15 +2359,15 @@
       </c>
       <c r="AM11" s="12">
         <f>AJ6+AJ7+AJ8+AJ11+AJ12+AJ13+AJ15+AJ19+AJ20+AJ21+AJ22+AJ23+AJ24+AJ25+AJ26+AJ28</f>
-        <v>166</v>
+        <v>323</v>
       </c>
       <c r="AN11" s="12">
         <f>AJ5+AJ9+AJ10+AJ14+AJ16+AJ17+AJ18+AJ27</f>
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="AO11" s="12">
         <f>AM11+AN11</f>
-        <v>247</v>
+        <v>476</v>
       </c>
     </row>
     <row r="12" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -2222,7 +2390,7 @@
       <c r="G12" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H12" s="32"/>
+      <c r="H12" s="31"/>
       <c r="I12" s="22" t="s">
         <v>125</v>
       </c>
@@ -2238,8 +2406,8 @@
       <c r="M12" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N12" s="35"/>
-      <c r="O12" s="32"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="31"/>
       <c r="P12" s="11" t="s">
         <v>125</v>
       </c>
@@ -2258,42 +2426,66 @@
       <c r="U12" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V12" s="32"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="24"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="11"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="32"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="24"/>
-      <c r="AG12" s="11"/>
-      <c r="AH12" s="11"/>
-      <c r="AI12" s="11"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="X12" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y12" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z12" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA12" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB12" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI12" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ12" s="5">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="AM12" s="12">
         <f>AM11/AM10</f>
-        <v>0.33603238866396762</v>
+        <v>0.65384615384615385</v>
       </c>
       <c r="AN12" s="12">
         <f>AN11/AN10</f>
-        <v>0.14835164835164835</v>
+        <v>0.28021978021978022</v>
       </c>
       <c r="AO12" s="12">
         <f>AO11/AO10</f>
-        <v>0.23749999999999999</v>
+        <v>0.45769230769230768</v>
       </c>
     </row>
     <row r="13" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -2316,7 +2508,7 @@
       <c r="G13" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="31"/>
       <c r="I13" s="22" t="s">
         <v>125</v>
       </c>
@@ -2332,8 +2524,8 @@
       <c r="M13" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N13" s="35"/>
-      <c r="O13" s="32"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="31"/>
       <c r="P13" s="11" t="s">
         <v>126</v>
       </c>
@@ -2352,27 +2544,51 @@
       <c r="U13" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V13" s="32"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="11"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="32"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="24"/>
-      <c r="AG13" s="11"/>
-      <c r="AH13" s="11"/>
-      <c r="AI13" s="11"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="X13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI13" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ13" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AL13" s="3"/>
       <c r="AM13" s="17"/>
@@ -2399,7 +2615,7 @@
       <c r="G14" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H14" s="32"/>
+      <c r="H14" s="31"/>
       <c r="I14" s="22" t="s">
         <v>126</v>
       </c>
@@ -2415,8 +2631,8 @@
       <c r="M14" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N14" s="35"/>
-      <c r="O14" s="32"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="31"/>
       <c r="P14" s="11" t="s">
         <v>125</v>
       </c>
@@ -2435,23 +2651,47 @@
       <c r="U14" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V14" s="32"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="11"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="32"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="11"/>
-      <c r="AH14" s="11"/>
-      <c r="AI14" s="11"/>
+      <c r="V14" s="31"/>
+      <c r="W14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC14" s="31"/>
+      <c r="AD14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI14" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ14" s="5">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="3"/>
@@ -2482,7 +2722,7 @@
       <c r="G15" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="31"/>
       <c r="I15" s="22" t="s">
         <v>125</v>
       </c>
@@ -2498,8 +2738,8 @@
       <c r="M15" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N15" s="35"/>
-      <c r="O15" s="32"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="31"/>
       <c r="P15" s="11" t="s">
         <v>125</v>
       </c>
@@ -2518,27 +2758,51 @@
       <c r="U15" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V15" s="32"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="11"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="32"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="11"/>
-      <c r="AH15" s="11"/>
-      <c r="AI15" s="11"/>
+      <c r="V15" s="31"/>
+      <c r="W15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA15" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC15" s="31"/>
+      <c r="AD15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI15" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ15" s="5">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
@@ -2565,7 +2829,7 @@
       <c r="G16" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="31"/>
       <c r="I16" s="22" t="s">
         <v>125</v>
       </c>
@@ -2581,8 +2845,8 @@
       <c r="M16" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N16" s="35"/>
-      <c r="O16" s="32"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="31"/>
       <c r="P16" s="11" t="s">
         <v>125</v>
       </c>
@@ -2601,34 +2865,58 @@
       <c r="U16" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V16" s="32"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="11"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="32"/>
-      <c r="AD16" s="11"/>
-      <c r="AE16" s="11"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="11"/>
-      <c r="AH16" s="11"/>
-      <c r="AI16" s="11"/>
+      <c r="V16" s="31"/>
+      <c r="W16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC16" s="31"/>
+      <c r="AD16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI16" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ16" s="5">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="AL16" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL16" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="26"/>
-      <c r="AN16" s="26"/>
-      <c r="AO16" s="27"/>
+      <c r="AM16" s="25"/>
+      <c r="AN16" s="25"/>
+      <c r="AO16" s="26"/>
     </row>
     <row r="17" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -2650,7 +2938,7 @@
       <c r="G17" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H17" s="32"/>
+      <c r="H17" s="31"/>
       <c r="I17" s="22" t="s">
         <v>126</v>
       </c>
@@ -2666,8 +2954,8 @@
       <c r="M17" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N17" s="35"/>
-      <c r="O17" s="32"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="31"/>
       <c r="P17" s="11" t="s">
         <v>125</v>
       </c>
@@ -2686,27 +2974,51 @@
       <c r="U17" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V17" s="32"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="11"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="32"/>
-      <c r="AD17" s="11"/>
-      <c r="AE17" s="11"/>
-      <c r="AF17" s="24"/>
-      <c r="AG17" s="11"/>
-      <c r="AH17" s="11"/>
-      <c r="AI17" s="11"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="X17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC17" s="31"/>
+      <c r="AD17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI17" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ17" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AL17" s="5" t="s">
         <v>12</v>
@@ -2741,7 +3053,7 @@
       <c r="G18" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="31"/>
       <c r="I18" s="22" t="s">
         <v>125</v>
       </c>
@@ -2757,8 +3069,8 @@
       <c r="M18" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N18" s="35"/>
-      <c r="O18" s="32"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="31"/>
       <c r="P18" s="11" t="s">
         <v>125</v>
       </c>
@@ -2777,27 +3089,51 @@
       <c r="U18" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V18" s="32"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="11"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="32"/>
-      <c r="AD18" s="11"/>
-      <c r="AE18" s="11"/>
-      <c r="AF18" s="24"/>
-      <c r="AG18" s="11"/>
-      <c r="AH18" s="11"/>
-      <c r="AI18" s="11"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="X18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI18" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="AJ18" s="5">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AL18" s="5" t="s">
         <v>16</v>
@@ -2835,7 +3171,7 @@
       <c r="G19" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="31"/>
       <c r="I19" s="22" t="s">
         <v>125</v>
       </c>
@@ -2851,8 +3187,8 @@
       <c r="M19" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N19" s="35"/>
-      <c r="O19" s="32"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="31"/>
       <c r="P19" s="11" t="s">
         <v>126</v>
       </c>
@@ -2871,42 +3207,66 @@
       <c r="U19" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V19" s="32"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="24"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="32"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="24"/>
-      <c r="AG19" s="11"/>
-      <c r="AH19" s="11"/>
-      <c r="AI19" s="11"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="X19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC19" s="31"/>
+      <c r="AD19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI19" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="AJ19" s="5">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AL19" s="5" t="s">
         <v>19</v>
       </c>
       <c r="AM19" s="12">
         <f>AM18-AM11</f>
-        <v>328</v>
+        <v>171</v>
       </c>
       <c r="AN19" s="12">
         <f>AN18-AN11</f>
-        <v>465</v>
+        <v>393</v>
       </c>
       <c r="AO19" s="12">
         <f>AM19+AN19</f>
-        <v>793</v>
+        <v>564</v>
       </c>
     </row>
     <row r="20" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -2929,7 +3289,7 @@
       <c r="G20" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="31"/>
       <c r="I20" s="22" t="s">
         <v>125</v>
       </c>
@@ -2945,8 +3305,8 @@
       <c r="M20" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N20" s="35"/>
-      <c r="O20" s="32"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="31"/>
       <c r="P20" s="11" t="s">
         <v>125</v>
       </c>
@@ -2965,42 +3325,66 @@
       <c r="U20" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V20" s="32"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="11"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="32"/>
-      <c r="AD20" s="11"/>
-      <c r="AE20" s="11"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="11"/>
-      <c r="AH20" s="11"/>
-      <c r="AI20" s="11"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA20" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB20" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC20" s="31"/>
+      <c r="AD20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI20" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ20" s="5">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AM20" s="20">
         <f>AM19/AM18</f>
-        <v>0.66396761133603244</v>
+        <v>0.34615384615384615</v>
       </c>
       <c r="AN20" s="20">
         <f>AN19/AN18</f>
-        <v>0.85164835164835162</v>
+        <v>0.71978021978021978</v>
       </c>
       <c r="AO20" s="20">
         <f>AO19/AO18</f>
-        <v>0.76249999999999996</v>
+        <v>0.54230769230769227</v>
       </c>
     </row>
     <row r="21" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3023,7 +3407,7 @@
       <c r="G21" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H21" s="32"/>
+      <c r="H21" s="31"/>
       <c r="I21" s="22" t="s">
         <v>125</v>
       </c>
@@ -3039,8 +3423,8 @@
       <c r="M21" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N21" s="35"/>
-      <c r="O21" s="32"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="31"/>
       <c r="P21" s="11" t="s">
         <v>125</v>
       </c>
@@ -3059,23 +3443,47 @@
       <c r="U21" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V21" s="32"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="11"/>
-      <c r="AA21" s="11"/>
-      <c r="AB21" s="11"/>
-      <c r="AC21" s="32"/>
-      <c r="AD21" s="11"/>
-      <c r="AE21" s="11"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="11"/>
-      <c r="AH21" s="11"/>
-      <c r="AI21" s="11"/>
+      <c r="V21" s="31"/>
+      <c r="W21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC21" s="31"/>
+      <c r="AD21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI21" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ21" s="5">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="3"/>
@@ -3102,7 +3510,7 @@
       <c r="G22" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H22" s="32"/>
+      <c r="H22" s="31"/>
       <c r="I22" s="22" t="s">
         <v>125</v>
       </c>
@@ -3118,8 +3526,8 @@
       <c r="M22" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N22" s="35"/>
-      <c r="O22" s="32"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="31"/>
       <c r="P22" s="11" t="s">
         <v>125</v>
       </c>
@@ -3138,23 +3546,47 @@
       <c r="U22" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V22" s="32"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="11"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="32"/>
-      <c r="AD22" s="11"/>
-      <c r="AE22" s="11"/>
-      <c r="AF22" s="24"/>
-      <c r="AG22" s="11"/>
-      <c r="AH22" s="11"/>
-      <c r="AI22" s="11"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC22" s="31"/>
+      <c r="AD22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI22" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ22" s="5">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="3"/>
@@ -3181,7 +3613,7 @@
       <c r="G23" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H23" s="32"/>
+      <c r="H23" s="31"/>
       <c r="I23" s="22" t="s">
         <v>125</v>
       </c>
@@ -3197,8 +3629,8 @@
       <c r="M23" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N23" s="35"/>
-      <c r="O23" s="32"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="31"/>
       <c r="P23" s="11" t="s">
         <v>125</v>
       </c>
@@ -3217,23 +3649,47 @@
       <c r="U23" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V23" s="32"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="11"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="32"/>
-      <c r="AD23" s="11"/>
-      <c r="AE23" s="11"/>
-      <c r="AF23" s="24"/>
-      <c r="AG23" s="11"/>
-      <c r="AH23" s="11"/>
-      <c r="AI23" s="11"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI23" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ23" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="3"/>
@@ -3260,7 +3716,7 @@
       <c r="G24" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H24" s="32"/>
+      <c r="H24" s="31"/>
       <c r="I24" s="22" t="s">
         <v>125</v>
       </c>
@@ -3276,8 +3732,8 @@
       <c r="M24" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N24" s="35"/>
-      <c r="O24" s="32"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="31"/>
       <c r="P24" s="11" t="s">
         <v>125</v>
       </c>
@@ -3296,23 +3752,47 @@
       <c r="U24" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V24" s="32"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="24"/>
-      <c r="Z24" s="11"/>
-      <c r="AA24" s="11"/>
-      <c r="AB24" s="11"/>
-      <c r="AC24" s="32"/>
-      <c r="AD24" s="11"/>
-      <c r="AE24" s="11"/>
-      <c r="AF24" s="24"/>
-      <c r="AG24" s="11"/>
-      <c r="AH24" s="11"/>
-      <c r="AI24" s="11"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC24" s="31"/>
+      <c r="AD24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI24" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ24" s="5">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="3"/>
@@ -3339,7 +3819,7 @@
       <c r="G25" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H25" s="32"/>
+      <c r="H25" s="31"/>
       <c r="I25" s="22" t="s">
         <v>125</v>
       </c>
@@ -3355,8 +3835,8 @@
       <c r="M25" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N25" s="35"/>
-      <c r="O25" s="32"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="31"/>
       <c r="P25" s="11" t="s">
         <v>125</v>
       </c>
@@ -3375,23 +3855,47 @@
       <c r="U25" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V25" s="32"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="11"/>
-      <c r="AB25" s="11"/>
-      <c r="AC25" s="32"/>
-      <c r="AD25" s="11"/>
-      <c r="AE25" s="11"/>
-      <c r="AF25" s="24"/>
-      <c r="AG25" s="11"/>
-      <c r="AH25" s="11"/>
-      <c r="AI25" s="11"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC25" s="31"/>
+      <c r="AD25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI25" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ25" s="5">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="3"/>
@@ -3418,7 +3922,7 @@
       <c r="G26" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H26" s="32"/>
+      <c r="H26" s="31"/>
       <c r="I26" s="22" t="s">
         <v>125</v>
       </c>
@@ -3434,8 +3938,8 @@
       <c r="M26" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N26" s="35"/>
-      <c r="O26" s="32"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="31"/>
       <c r="P26" s="11" t="s">
         <v>125</v>
       </c>
@@ -3454,27 +3958,51 @@
       <c r="U26" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V26" s="32"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="24"/>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="11"/>
-      <c r="AB26" s="11"/>
-      <c r="AC26" s="32"/>
-      <c r="AD26" s="11"/>
-      <c r="AE26" s="11"/>
-      <c r="AF26" s="24"/>
-      <c r="AG26" s="11"/>
-      <c r="AH26" s="11"/>
-      <c r="AI26" s="11"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH26" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI26" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="AJ26" s="5">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3497,7 +4025,7 @@
       <c r="G27" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="31"/>
       <c r="I27" s="22" t="s">
         <v>125</v>
       </c>
@@ -3508,13 +4036,13 @@
         <v>126</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M27" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N27" s="35"/>
-      <c r="O27" s="32"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="31"/>
       <c r="P27" s="11" t="s">
         <v>125</v>
       </c>
@@ -3533,23 +4061,47 @@
       <c r="U27" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V27" s="32"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="11"/>
-      <c r="AA27" s="11"/>
-      <c r="AB27" s="11"/>
-      <c r="AC27" s="32"/>
-      <c r="AD27" s="11"/>
-      <c r="AE27" s="11"/>
-      <c r="AF27" s="24"/>
-      <c r="AG27" s="11"/>
-      <c r="AH27" s="11"/>
-      <c r="AI27" s="11"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA27" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC27" s="31"/>
+      <c r="AD27" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE27" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI27" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ27" s="5">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="3"/>
@@ -3576,7 +4128,7 @@
       <c r="G28" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H28" s="33"/>
+      <c r="H28" s="32"/>
       <c r="I28" s="22" t="s">
         <v>125</v>
       </c>
@@ -3592,8 +4144,8 @@
       <c r="M28" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N28" s="36"/>
-      <c r="O28" s="33"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="32"/>
       <c r="P28" s="11" t="s">
         <v>126</v>
       </c>
@@ -3612,27 +4164,51 @@
       <c r="U28" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V28" s="33"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="11"/>
-      <c r="AB28" s="11"/>
-      <c r="AC28" s="33"/>
-      <c r="AD28" s="11"/>
-      <c r="AE28" s="11"/>
-      <c r="AF28" s="24"/>
-      <c r="AG28" s="11"/>
-      <c r="AH28" s="11"/>
-      <c r="AI28" s="11"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z28" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI28" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ28" s="5">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
@@ -3757,97 +4333,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="38"/>
-      <c r="AC1" s="38"/>
-      <c r="AD1" s="38"/>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="38"/>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="38"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="37"/>
-      <c r="AF2" s="37"/>
-      <c r="AG2" s="37"/>
-      <c r="AH2" s="37"/>
-      <c r="AI2" s="37"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="27" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -3970,25 +4546,25 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AJ3" s="30" t="s">
+      <c r="AJ3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="30" t="s">
+      <c r="AK3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="25" t="s">
+      <c r="AL3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="26"/>
+      <c r="AM3" s="25"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
       <c r="F4" s="21">
         <v>45597</v>
       </c>
@@ -4079,8 +4655,8 @@
       <c r="AI4" s="21">
         <v>45626</v>
       </c>
-      <c r="AJ4" s="30"/>
-      <c r="AK4" s="30"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="29"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -4110,7 +4686,7 @@
       <c r="G5" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="H5" s="30" t="s">
         <v>131</v>
       </c>
       <c r="I5" s="22" t="s">
@@ -4128,10 +4704,10 @@
       <c r="M5" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N5" s="39" t="s">
+      <c r="N5" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="O5" s="31" t="s">
+      <c r="O5" s="30" t="s">
         <v>131</v>
       </c>
       <c r="P5" s="11" t="s">
@@ -4152,27 +4728,51 @@
       <c r="U5" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V5" s="31" t="s">
+      <c r="V5" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="24"/>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="11"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="31" t="s">
+      <c r="W5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC5" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="11"/>
-      <c r="AF5" s="24"/>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="11"/>
+      <c r="AD5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI5" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ5" s="5">
         <f t="shared" ref="AJ5:AJ36" si="1">COUNTIF(F5:AI5,"P")</f>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK36" si="2">COUNTIF(F5:AI5,"A")</f>
@@ -4209,7 +4809,7 @@
       <c r="G6" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H6" s="32"/>
+      <c r="H6" s="31"/>
       <c r="I6" s="22" t="s">
         <v>125</v>
       </c>
@@ -4225,8 +4825,8 @@
       <c r="M6" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N6" s="40"/>
-      <c r="O6" s="32"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="31"/>
       <c r="P6" s="11" t="s">
         <v>125</v>
       </c>
@@ -4245,27 +4845,51 @@
       <c r="U6" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V6" s="32"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="24"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="11"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="11"/>
-      <c r="AE6" s="11"/>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="11"/>
-      <c r="AH6" s="11"/>
-      <c r="AI6" s="11"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI6" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="AJ6" s="5">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AL6" s="5" t="s">
         <v>10</v>
@@ -4296,7 +4920,7 @@
       <c r="G7" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H7" s="32"/>
+      <c r="H7" s="31"/>
       <c r="I7" s="22" t="s">
         <v>125</v>
       </c>
@@ -4312,8 +4936,8 @@
       <c r="M7" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N7" s="40"/>
-      <c r="O7" s="32"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="31"/>
       <c r="P7" s="11" t="s">
         <v>125</v>
       </c>
@@ -4332,27 +4956,51 @@
       <c r="U7" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V7" s="32"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="24"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="11"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="32"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="24"/>
-      <c r="AG7" s="11"/>
-      <c r="AH7" s="11"/>
-      <c r="AI7" s="11"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y7" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC7" s="31"/>
+      <c r="AD7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI7" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ7" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AK7" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
@@ -4379,7 +5027,7 @@
       <c r="G8" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H8" s="32"/>
+      <c r="H8" s="31"/>
       <c r="I8" s="22" t="s">
         <v>126</v>
       </c>
@@ -4395,8 +5043,8 @@
       <c r="M8" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N8" s="40"/>
-      <c r="O8" s="32"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="31"/>
       <c r="P8" s="11" t="s">
         <v>125</v>
       </c>
@@ -4415,34 +5063,58 @@
       <c r="U8" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V8" s="32"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="11"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="32"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="11"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="11"/>
-      <c r="AH8" s="11"/>
-      <c r="AI8" s="11"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z8" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB8" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI8" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ8" s="5">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AK8" s="5">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="AL8" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="26"/>
-      <c r="AN8" s="26"/>
-      <c r="AO8" s="27"/>
+      <c r="AM8" s="25"/>
+      <c r="AN8" s="25"/>
+      <c r="AO8" s="26"/>
     </row>
     <row r="9" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -4464,7 +5136,7 @@
       <c r="G9" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H9" s="32"/>
+      <c r="H9" s="31"/>
       <c r="I9" s="22" t="s">
         <v>125</v>
       </c>
@@ -4480,8 +5152,8 @@
       <c r="M9" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N9" s="40"/>
-      <c r="O9" s="32"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="31"/>
       <c r="P9" s="11" t="s">
         <v>125</v>
       </c>
@@ -4500,27 +5172,51 @@
       <c r="U9" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V9" s="32"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="11"/>
-      <c r="AA9" s="11"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="32"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="24"/>
-      <c r="AG9" s="11"/>
-      <c r="AH9" s="11"/>
-      <c r="AI9" s="11"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="X9" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y9" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA9" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB9" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI9" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ9" s="5">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AK9" s="5">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AL9" s="5" t="s">
         <v>12</v>
@@ -4555,7 +5251,7 @@
       <c r="G10" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="31"/>
       <c r="I10" s="22" t="s">
         <v>125</v>
       </c>
@@ -4571,8 +5267,8 @@
       <c r="M10" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N10" s="40"/>
-      <c r="O10" s="32"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="31"/>
       <c r="P10" s="11" t="s">
         <v>125</v>
       </c>
@@ -4591,23 +5287,47 @@
       <c r="U10" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V10" s="32"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="11"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="32"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="24"/>
-      <c r="AG10" s="11"/>
-      <c r="AH10" s="11"/>
-      <c r="AI10" s="11"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI10" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ10" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="2"/>
@@ -4649,7 +5369,7 @@
       <c r="G11" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="31"/>
       <c r="I11" s="22" t="s">
         <v>125</v>
       </c>
@@ -4665,8 +5385,8 @@
       <c r="M11" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N11" s="40"/>
-      <c r="O11" s="32"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="31"/>
       <c r="P11" s="11" t="s">
         <v>125</v>
       </c>
@@ -4685,42 +5405,66 @@
       <c r="U11" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V11" s="32"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="24"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="11"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="32"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="24"/>
-      <c r="AG11" s="11"/>
-      <c r="AH11" s="11"/>
-      <c r="AI11" s="11"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA11" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI11" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ11" s="5">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="AM11" s="12">
         <f>+AJ7+AJ18</f>
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="AN11" s="12">
         <f>AJ5+AJ6+AJ8+AJ9+AJ10+AJ11+AJ12+AJ13+AJ14+AJ15+AJ16+AJ17+AJ19+AJ20</f>
-        <v>149</v>
+        <v>300</v>
       </c>
       <c r="AO11" s="12">
         <f>AM11+AN11</f>
-        <v>175</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -4743,7 +5487,7 @@
       <c r="G12" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H12" s="32"/>
+      <c r="H12" s="31"/>
       <c r="I12" s="22" t="s">
         <v>126</v>
       </c>
@@ -4759,8 +5503,8 @@
       <c r="M12" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N12" s="40"/>
-      <c r="O12" s="32"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="31"/>
       <c r="P12" s="11" t="s">
         <v>125</v>
       </c>
@@ -4779,23 +5523,47 @@
       <c r="U12" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V12" s="32"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="24"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="11"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="32"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="24"/>
-      <c r="AG12" s="11"/>
-      <c r="AH12" s="11"/>
-      <c r="AI12" s="11"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI12" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ12" s="5">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="2"/>
@@ -4806,15 +5574,15 @@
       </c>
       <c r="AM12" s="12">
         <f>AM11/AM10</f>
-        <v>5.2631578947368418E-2</v>
+        <v>9.9190283400809723E-2</v>
       </c>
       <c r="AN12" s="12">
         <f>AN11/AN10</f>
-        <v>0.27289377289377287</v>
+        <v>0.5494505494505495</v>
       </c>
       <c r="AO12" s="12">
         <f>AO11/AO10</f>
-        <v>0.16826923076923078</v>
+        <v>0.33557692307692305</v>
       </c>
     </row>
     <row r="13" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -4837,7 +5605,7 @@
       <c r="G13" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="31"/>
       <c r="I13" s="22" t="s">
         <v>125</v>
       </c>
@@ -4853,8 +5621,8 @@
       <c r="M13" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N13" s="40"/>
-      <c r="O13" s="32"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="31"/>
       <c r="P13" s="11" t="s">
         <v>125</v>
       </c>
@@ -4873,23 +5641,47 @@
       <c r="U13" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V13" s="32"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="11"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="32"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="24"/>
-      <c r="AG13" s="11"/>
-      <c r="AH13" s="11"/>
-      <c r="AI13" s="11"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI13" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ13" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="2"/>
@@ -4920,7 +5712,7 @@
       <c r="G14" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H14" s="32"/>
+      <c r="H14" s="31"/>
       <c r="I14" s="22" t="s">
         <v>125</v>
       </c>
@@ -4936,8 +5728,8 @@
       <c r="M14" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N14" s="40"/>
-      <c r="O14" s="32"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="31"/>
       <c r="P14" s="11" t="s">
         <v>125</v>
       </c>
@@ -4956,23 +5748,47 @@
       <c r="U14" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V14" s="32"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="11"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="32"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="11"/>
-      <c r="AH14" s="11"/>
-      <c r="AI14" s="11"/>
+      <c r="V14" s="31"/>
+      <c r="W14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC14" s="31"/>
+      <c r="AD14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI14" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ14" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="2"/>
@@ -5003,7 +5819,7 @@
       <c r="G15" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="31"/>
       <c r="I15" s="22" t="s">
         <v>125</v>
       </c>
@@ -5019,8 +5835,8 @@
       <c r="M15" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N15" s="40"/>
-      <c r="O15" s="32"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="31"/>
       <c r="P15" s="11" t="s">
         <v>125</v>
       </c>
@@ -5039,27 +5855,51 @@
       <c r="U15" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V15" s="32"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="11"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="32"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="11"/>
-      <c r="AH15" s="11"/>
-      <c r="AI15" s="11"/>
+      <c r="V15" s="31"/>
+      <c r="W15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA15" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC15" s="31"/>
+      <c r="AD15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF15" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI15" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ15" s="5">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
@@ -5086,7 +5926,7 @@
       <c r="G16" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="31"/>
       <c r="I16" s="22" t="s">
         <v>125</v>
       </c>
@@ -5102,8 +5942,8 @@
       <c r="M16" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N16" s="40"/>
-      <c r="O16" s="32"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="31"/>
       <c r="P16" s="11" t="s">
         <v>125</v>
       </c>
@@ -5122,34 +5962,58 @@
       <c r="U16" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V16" s="32"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="11"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="32"/>
-      <c r="AD16" s="11"/>
-      <c r="AE16" s="11"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="11"/>
-      <c r="AH16" s="11"/>
-      <c r="AI16" s="11"/>
+      <c r="V16" s="31"/>
+      <c r="W16" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC16" s="31"/>
+      <c r="AD16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI16" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ16" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AL16" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL16" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="26"/>
-      <c r="AN16" s="26"/>
-      <c r="AO16" s="27"/>
+      <c r="AM16" s="25"/>
+      <c r="AN16" s="25"/>
+      <c r="AO16" s="26"/>
     </row>
     <row r="17" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -5171,7 +6035,7 @@
       <c r="G17" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H17" s="32"/>
+      <c r="H17" s="31"/>
       <c r="I17" s="22" t="s">
         <v>125</v>
       </c>
@@ -5187,8 +6051,8 @@
       <c r="M17" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N17" s="40"/>
-      <c r="O17" s="32"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="31"/>
       <c r="P17" s="11" t="s">
         <v>126</v>
       </c>
@@ -5207,23 +6071,47 @@
       <c r="U17" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V17" s="32"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="11"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="32"/>
-      <c r="AD17" s="11"/>
-      <c r="AE17" s="11"/>
-      <c r="AF17" s="24"/>
-      <c r="AG17" s="11"/>
-      <c r="AH17" s="11"/>
-      <c r="AI17" s="11"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC17" s="31"/>
+      <c r="AD17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI17" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ17" s="5">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="2"/>
@@ -5262,7 +6150,7 @@
       <c r="G18" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="31"/>
       <c r="I18" s="22" t="s">
         <v>125</v>
       </c>
@@ -5278,8 +6166,8 @@
       <c r="M18" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N18" s="40"/>
-      <c r="O18" s="32"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="31"/>
       <c r="P18" s="11" t="s">
         <v>125</v>
       </c>
@@ -5298,23 +6186,47 @@
       <c r="U18" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V18" s="32"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="11"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="32"/>
-      <c r="AD18" s="11"/>
-      <c r="AE18" s="11"/>
-      <c r="AF18" s="24"/>
-      <c r="AG18" s="11"/>
-      <c r="AH18" s="11"/>
-      <c r="AI18" s="11"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI18" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ18" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="2"/>
@@ -5356,7 +6268,7 @@
       <c r="G19" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="31"/>
       <c r="I19" s="22" t="s">
         <v>125</v>
       </c>
@@ -5372,8 +6284,8 @@
       <c r="M19" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N19" s="40"/>
-      <c r="O19" s="32"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="31"/>
       <c r="P19" s="11" t="s">
         <v>125</v>
       </c>
@@ -5392,42 +6304,66 @@
       <c r="U19" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V19" s="32"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="24"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="32"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="24"/>
-      <c r="AG19" s="11"/>
-      <c r="AH19" s="11"/>
-      <c r="AI19" s="11"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC19" s="31"/>
+      <c r="AD19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI19" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ19" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL19" s="5" t="s">
         <v>19</v>
       </c>
       <c r="AM19" s="12">
         <f>AM18-AM11</f>
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="AN19" s="12">
         <f>AN18-AN11</f>
-        <v>397</v>
+        <v>246</v>
       </c>
       <c r="AO19" s="12">
         <f>AM19+AN19</f>
-        <v>865</v>
+        <v>691</v>
       </c>
     </row>
     <row r="20" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5450,7 +6386,7 @@
       <c r="G20" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="31"/>
       <c r="I20" s="22" t="s">
         <v>125</v>
       </c>
@@ -5466,8 +6402,8 @@
       <c r="M20" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N20" s="40"/>
-      <c r="O20" s="32"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="31"/>
       <c r="P20" s="11" t="s">
         <v>125</v>
       </c>
@@ -5486,23 +6422,47 @@
       <c r="U20" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V20" s="32"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="11"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="32"/>
-      <c r="AD20" s="11"/>
-      <c r="AE20" s="11"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="11"/>
-      <c r="AH20" s="11"/>
-      <c r="AI20" s="11"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC20" s="31"/>
+      <c r="AD20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI20" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ20" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="2"/>
@@ -5513,15 +6473,15 @@
       </c>
       <c r="AM20" s="20">
         <f>AM19/AM18</f>
-        <v>0.94736842105263153</v>
+        <v>0.90080971659919029</v>
       </c>
       <c r="AN20" s="20">
         <f>AN19/AN18</f>
-        <v>0.72710622710622708</v>
+        <v>0.45054945054945056</v>
       </c>
       <c r="AO20" s="20">
         <f>AO19/AO18</f>
-        <v>0.83173076923076927</v>
+        <v>0.66442307692307689</v>
       </c>
     </row>
     <row r="21" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5544,7 +6504,7 @@
       <c r="G21" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H21" s="32"/>
+      <c r="H21" s="31"/>
       <c r="I21" s="22" t="s">
         <v>125</v>
       </c>
@@ -5560,8 +6520,8 @@
       <c r="M21" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N21" s="40"/>
-      <c r="O21" s="32"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="31"/>
       <c r="P21" s="11" t="s">
         <v>125</v>
       </c>
@@ -5580,27 +6540,51 @@
       <c r="U21" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V21" s="32"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="11"/>
-      <c r="AA21" s="11"/>
-      <c r="AB21" s="11"/>
-      <c r="AC21" s="32"/>
-      <c r="AD21" s="11"/>
-      <c r="AE21" s="11"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="11"/>
-      <c r="AH21" s="11"/>
-      <c r="AI21" s="11"/>
+      <c r="V21" s="31"/>
+      <c r="W21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB21" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC21" s="31"/>
+      <c r="AD21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG21" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI21" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ21" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5623,7 +6607,7 @@
       <c r="G22" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H22" s="32"/>
+      <c r="H22" s="31"/>
       <c r="I22" s="22" t="s">
         <v>125</v>
       </c>
@@ -5639,8 +6623,8 @@
       <c r="M22" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N22" s="40"/>
-      <c r="O22" s="32"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="31"/>
       <c r="P22" s="11" t="s">
         <v>125</v>
       </c>
@@ -5659,23 +6643,47 @@
       <c r="U22" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V22" s="32"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="11"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="32"/>
-      <c r="AD22" s="11"/>
-      <c r="AE22" s="11"/>
-      <c r="AF22" s="24"/>
-      <c r="AG22" s="11"/>
-      <c r="AH22" s="11"/>
-      <c r="AI22" s="11"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC22" s="31"/>
+      <c r="AD22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI22" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ22" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="2"/>
@@ -5702,7 +6710,7 @@
       <c r="G23" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H23" s="32"/>
+      <c r="H23" s="31"/>
       <c r="I23" s="22" t="s">
         <v>125</v>
       </c>
@@ -5718,8 +6726,8 @@
       <c r="M23" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N23" s="40"/>
-      <c r="O23" s="32"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="31"/>
       <c r="P23" s="11" t="s">
         <v>125</v>
       </c>
@@ -5738,23 +6746,47 @@
       <c r="U23" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V23" s="32"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="11"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="32"/>
-      <c r="AD23" s="11"/>
-      <c r="AE23" s="11"/>
-      <c r="AF23" s="24"/>
-      <c r="AG23" s="11"/>
-      <c r="AH23" s="11"/>
-      <c r="AI23" s="11"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI23" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ23" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="2"/>
@@ -5781,7 +6813,7 @@
       <c r="G24" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H24" s="32"/>
+      <c r="H24" s="31"/>
       <c r="I24" s="22" t="s">
         <v>125</v>
       </c>
@@ -5797,8 +6829,8 @@
       <c r="M24" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N24" s="40"/>
-      <c r="O24" s="32"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="31"/>
       <c r="P24" s="11" t="s">
         <v>125</v>
       </c>
@@ -5817,27 +6849,51 @@
       <c r="U24" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V24" s="32"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="24"/>
-      <c r="Z24" s="11"/>
-      <c r="AA24" s="11"/>
-      <c r="AB24" s="11"/>
-      <c r="AC24" s="32"/>
-      <c r="AD24" s="11"/>
-      <c r="AE24" s="11"/>
-      <c r="AF24" s="24"/>
-      <c r="AG24" s="11"/>
-      <c r="AH24" s="11"/>
-      <c r="AI24" s="11"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC24" s="31"/>
+      <c r="AD24" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE24" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF24" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH24" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI24" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="AJ24" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5860,7 +6916,7 @@
       <c r="G25" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H25" s="32"/>
+      <c r="H25" s="31"/>
       <c r="I25" s="22" t="s">
         <v>125</v>
       </c>
@@ -5876,8 +6932,8 @@
       <c r="M25" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N25" s="40"/>
-      <c r="O25" s="32"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="31"/>
       <c r="P25" s="11" t="s">
         <v>126</v>
       </c>
@@ -5896,27 +6952,51 @@
       <c r="U25" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V25" s="32"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="11"/>
-      <c r="AB25" s="11"/>
-      <c r="AC25" s="32"/>
-      <c r="AD25" s="11"/>
-      <c r="AE25" s="11"/>
-      <c r="AF25" s="24"/>
-      <c r="AG25" s="11"/>
-      <c r="AH25" s="11"/>
-      <c r="AI25" s="11"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="X25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA25" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB25" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC25" s="31"/>
+      <c r="AD25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI25" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="AJ25" s="5">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5939,7 +7019,7 @@
       <c r="G26" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H26" s="32"/>
+      <c r="H26" s="31"/>
       <c r="I26" s="22" t="s">
         <v>125</v>
       </c>
@@ -5955,8 +7035,8 @@
       <c r="M26" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N26" s="40"/>
-      <c r="O26" s="32"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="31"/>
       <c r="P26" s="11" t="s">
         <v>125</v>
       </c>
@@ -5975,23 +7055,47 @@
       <c r="U26" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V26" s="32"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="24"/>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="11"/>
-      <c r="AB26" s="11"/>
-      <c r="AC26" s="32"/>
-      <c r="AD26" s="11"/>
-      <c r="AE26" s="11"/>
-      <c r="AF26" s="24"/>
-      <c r="AG26" s="11"/>
-      <c r="AH26" s="11"/>
-      <c r="AI26" s="11"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI26" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ26" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="2"/>
@@ -6018,7 +7122,7 @@
       <c r="G27" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="31"/>
       <c r="I27" s="22" t="s">
         <v>125</v>
       </c>
@@ -6034,8 +7138,8 @@
       <c r="M27" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N27" s="40"/>
-      <c r="O27" s="32"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="31"/>
       <c r="P27" s="11" t="s">
         <v>125</v>
       </c>
@@ -6054,23 +7158,47 @@
       <c r="U27" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V27" s="32"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="11"/>
-      <c r="AA27" s="11"/>
-      <c r="AB27" s="11"/>
-      <c r="AC27" s="32"/>
-      <c r="AD27" s="11"/>
-      <c r="AE27" s="11"/>
-      <c r="AF27" s="24"/>
-      <c r="AG27" s="11"/>
-      <c r="AH27" s="11"/>
-      <c r="AI27" s="11"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC27" s="31"/>
+      <c r="AD27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI27" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ27" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="2"/>
@@ -6097,7 +7225,7 @@
       <c r="G28" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H28" s="32"/>
+      <c r="H28" s="31"/>
       <c r="I28" s="22" t="s">
         <v>125</v>
       </c>
@@ -6113,8 +7241,8 @@
       <c r="M28" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N28" s="40"/>
-      <c r="O28" s="32"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="31"/>
       <c r="P28" s="11" t="s">
         <v>125</v>
       </c>
@@ -6133,23 +7261,47 @@
       <c r="U28" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V28" s="32"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="11"/>
-      <c r="AB28" s="11"/>
-      <c r="AC28" s="32"/>
-      <c r="AD28" s="11"/>
-      <c r="AE28" s="11"/>
-      <c r="AF28" s="24"/>
-      <c r="AG28" s="11"/>
-      <c r="AH28" s="11"/>
-      <c r="AI28" s="11"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI28" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ28" s="5">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="2"/>
@@ -6176,7 +7328,7 @@
       <c r="G29" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H29" s="32"/>
+      <c r="H29" s="31"/>
       <c r="I29" s="22" t="s">
         <v>125</v>
       </c>
@@ -6192,8 +7344,8 @@
       <c r="M29" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N29" s="40"/>
-      <c r="O29" s="32"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="31"/>
       <c r="P29" s="11" t="s">
         <v>125</v>
       </c>
@@ -6212,23 +7364,47 @@
       <c r="U29" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V29" s="32"/>
-      <c r="W29" s="11"/>
-      <c r="X29" s="11"/>
-      <c r="Y29" s="24"/>
-      <c r="Z29" s="11"/>
-      <c r="AA29" s="11"/>
-      <c r="AB29" s="11"/>
-      <c r="AC29" s="32"/>
-      <c r="AD29" s="11"/>
-      <c r="AE29" s="11"/>
-      <c r="AF29" s="24"/>
-      <c r="AG29" s="11"/>
-      <c r="AH29" s="11"/>
-      <c r="AI29" s="11"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI29" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ29" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="2"/>
@@ -6255,7 +7431,7 @@
       <c r="G30" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H30" s="32"/>
+      <c r="H30" s="31"/>
       <c r="I30" s="22" t="s">
         <v>125</v>
       </c>
@@ -6271,8 +7447,8 @@
       <c r="M30" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N30" s="40"/>
-      <c r="O30" s="32"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="31"/>
       <c r="P30" s="11" t="s">
         <v>125</v>
       </c>
@@ -6291,27 +7467,51 @@
       <c r="U30" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V30" s="32"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="24"/>
-      <c r="Z30" s="11"/>
-      <c r="AA30" s="11"/>
-      <c r="AB30" s="11"/>
-      <c r="AC30" s="32"/>
-      <c r="AD30" s="11"/>
-      <c r="AE30" s="11"/>
-      <c r="AF30" s="24"/>
-      <c r="AG30" s="11"/>
-      <c r="AH30" s="11"/>
-      <c r="AI30" s="11"/>
+      <c r="V30" s="31"/>
+      <c r="W30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y30" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG30" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI30" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ30" s="5">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -6334,7 +7534,7 @@
       <c r="G31" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H31" s="32"/>
+      <c r="H31" s="31"/>
       <c r="I31" s="22" t="s">
         <v>125</v>
       </c>
@@ -6350,8 +7550,8 @@
       <c r="M31" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N31" s="40"/>
-      <c r="O31" s="32"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="31"/>
       <c r="P31" s="11" t="s">
         <v>125</v>
       </c>
@@ -6370,23 +7570,47 @@
       <c r="U31" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V31" s="32"/>
-      <c r="W31" s="11"/>
-      <c r="X31" s="11"/>
-      <c r="Y31" s="24"/>
-      <c r="Z31" s="11"/>
-      <c r="AA31" s="11"/>
-      <c r="AB31" s="11"/>
-      <c r="AC31" s="32"/>
-      <c r="AD31" s="11"/>
-      <c r="AE31" s="11"/>
-      <c r="AF31" s="24"/>
-      <c r="AG31" s="11"/>
-      <c r="AH31" s="11"/>
-      <c r="AI31" s="11"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC31" s="31"/>
+      <c r="AD31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI31" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ31" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="2"/>
@@ -6413,7 +7637,7 @@
       <c r="G32" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H32" s="32"/>
+      <c r="H32" s="31"/>
       <c r="I32" s="22" t="s">
         <v>125</v>
       </c>
@@ -6429,8 +7653,8 @@
       <c r="M32" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N32" s="40"/>
-      <c r="O32" s="32"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="31"/>
       <c r="P32" s="11" t="s">
         <v>125</v>
       </c>
@@ -6449,27 +7673,51 @@
       <c r="U32" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V32" s="32"/>
-      <c r="W32" s="11"/>
-      <c r="X32" s="11"/>
-      <c r="Y32" s="24"/>
-      <c r="Z32" s="11"/>
-      <c r="AA32" s="11"/>
-      <c r="AB32" s="11"/>
-      <c r="AC32" s="32"/>
-      <c r="AD32" s="11"/>
-      <c r="AE32" s="11"/>
-      <c r="AF32" s="24"/>
-      <c r="AG32" s="11"/>
-      <c r="AH32" s="11"/>
-      <c r="AI32" s="11"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA32" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC32" s="31"/>
+      <c r="AD32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF32" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI32" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="AJ32" s="5">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:37" ht="16.5" x14ac:dyDescent="0.25">
@@ -6492,7 +7740,7 @@
       <c r="G33" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H33" s="32"/>
+      <c r="H33" s="31"/>
       <c r="I33" s="22" t="s">
         <v>125</v>
       </c>
@@ -6508,8 +7756,8 @@
       <c r="M33" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N33" s="40"/>
-      <c r="O33" s="32"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="31"/>
       <c r="P33" s="11" t="s">
         <v>125</v>
       </c>
@@ -6528,23 +7776,47 @@
       <c r="U33" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V33" s="32"/>
-      <c r="W33" s="11"/>
-      <c r="X33" s="11"/>
-      <c r="Y33" s="24"/>
-      <c r="Z33" s="11"/>
-      <c r="AA33" s="11"/>
-      <c r="AB33" s="11"/>
-      <c r="AC33" s="32"/>
-      <c r="AD33" s="11"/>
-      <c r="AE33" s="11"/>
-      <c r="AF33" s="24"/>
-      <c r="AG33" s="11"/>
-      <c r="AH33" s="11"/>
-      <c r="AI33" s="11"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC33" s="31"/>
+      <c r="AD33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH33" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI33" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ33" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK33" s="5">
         <f t="shared" si="2"/>
@@ -6571,7 +7843,7 @@
       <c r="G34" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H34" s="32"/>
+      <c r="H34" s="31"/>
       <c r="I34" s="22" t="s">
         <v>125</v>
       </c>
@@ -6587,8 +7859,8 @@
       <c r="M34" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N34" s="40"/>
-      <c r="O34" s="32"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="31"/>
       <c r="P34" s="11" t="s">
         <v>125</v>
       </c>
@@ -6607,23 +7879,47 @@
       <c r="U34" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V34" s="32"/>
-      <c r="W34" s="11"/>
-      <c r="X34" s="11"/>
-      <c r="Y34" s="24"/>
-      <c r="Z34" s="11"/>
-      <c r="AA34" s="11"/>
-      <c r="AB34" s="11"/>
-      <c r="AC34" s="32"/>
-      <c r="AD34" s="11"/>
-      <c r="AE34" s="11"/>
-      <c r="AF34" s="24"/>
-      <c r="AG34" s="11"/>
-      <c r="AH34" s="11"/>
-      <c r="AI34" s="11"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC34" s="31"/>
+      <c r="AD34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE34" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF34" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="AG34" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="AH34" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="AI34" s="11" t="s">
+        <v>133</v>
+      </c>
       <c r="AJ34" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AK34" s="5">
         <f t="shared" si="2"/>
@@ -6650,7 +7946,7 @@
       <c r="G35" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H35" s="32"/>
+      <c r="H35" s="31"/>
       <c r="I35" s="22" t="s">
         <v>125</v>
       </c>
@@ -6666,8 +7962,8 @@
       <c r="M35" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N35" s="40"/>
-      <c r="O35" s="32"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="31"/>
       <c r="P35" s="11" t="s">
         <v>125</v>
       </c>
@@ -6686,27 +7982,51 @@
       <c r="U35" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V35" s="32"/>
-      <c r="W35" s="11"/>
-      <c r="X35" s="11"/>
-      <c r="Y35" s="24"/>
-      <c r="Z35" s="11"/>
-      <c r="AA35" s="11"/>
-      <c r="AB35" s="11"/>
-      <c r="AC35" s="32"/>
-      <c r="AD35" s="11"/>
-      <c r="AE35" s="11"/>
-      <c r="AF35" s="24"/>
-      <c r="AG35" s="11"/>
-      <c r="AH35" s="11"/>
-      <c r="AI35" s="11"/>
+      <c r="V35" s="31"/>
+      <c r="W35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="X35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC35" s="31"/>
+      <c r="AD35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF35" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG35" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI35" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ35" s="5">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AK35" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="16.5" x14ac:dyDescent="0.25">
@@ -6729,7 +8049,7 @@
       <c r="G36" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H36" s="33"/>
+      <c r="H36" s="32"/>
       <c r="I36" s="22" t="s">
         <v>125</v>
       </c>
@@ -6745,8 +8065,8 @@
       <c r="M36" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="N36" s="41"/>
-      <c r="O36" s="33"/>
+      <c r="N36" s="40"/>
+      <c r="O36" s="32"/>
       <c r="P36" s="11" t="s">
         <v>125</v>
       </c>
@@ -6765,27 +8085,51 @@
       <c r="U36" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="V36" s="33"/>
-      <c r="W36" s="11"/>
-      <c r="X36" s="11"/>
-      <c r="Y36" s="24"/>
-      <c r="Z36" s="11"/>
-      <c r="AA36" s="11"/>
-      <c r="AB36" s="11"/>
-      <c r="AC36" s="33"/>
-      <c r="AD36" s="11"/>
-      <c r="AE36" s="11"/>
-      <c r="AF36" s="24"/>
-      <c r="AG36" s="11"/>
-      <c r="AH36" s="11"/>
-      <c r="AI36" s="11"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA36" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC36" s="32"/>
+      <c r="AD36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF36" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI36" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ36" s="5">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6813,12 +8157,12 @@
       <formula>F$4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AI5 F6:G36 I6:M36 P6:U36 W6:X36 Z6:AB36 AD6:AE36 AG6:AI36 AL4:AM4 AL5:AL6 AM9:AO9 AL9:AL12 AM17:AO17 AL17:AL20">
+  <conditionalFormatting sqref="F3:AI5 F6:G36 I6:M36 P6:U36 W6:AB36 AD6:AI36 AL4:AM4 AL5:AL6 AM9:AO9 AL9:AL12 AM17:AO17 AL17:AL20">
     <cfRule type="expression" dxfId="4" priority="11">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:AI5 F6:G36 I6:M36 P6:U36 W6:X36 Z6:AB36 AD6:AE36 AG6:AI36">
+  <conditionalFormatting sqref="F5:AI5 F6:G36 I6:M36 P6:U36 W6:AB36 AD6:AI36">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"L"</formula>
     </cfRule>
